--- a/src/test/resources/TestDriver/Hearst/ActivityData/CDB_PSD_20260731.xlsx
+++ b/src/test/resources/TestDriver/Hearst/ActivityData/CDB_PSD_20260731.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos\fyntrac-data\src\test\resources\TestDriver\Hearst\ActivityData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF30CF20-89A5-4DDB-B0F4-8CECE31D4B12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB48EB79-0473-4DC8-9923-F30D6D8FEB37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8558,9 +8558,6 @@
     <t>T38yripZf91</t>
   </si>
   <si>
-    <t>Y9B_nWQ6vmTg</t>
-  </si>
-  <si>
     <t>oXmkvAcI78iY</t>
   </si>
   <si>
@@ -10050,6 +10047,9 @@
   </si>
   <si>
     <t>M-CGMSDtOfi</t>
+  </si>
+  <si>
+    <t>uxYnTP0eRE</t>
   </si>
 </sst>
 </file>
@@ -10840,7 +10840,7 @@
         <v>46</v>
       </c>
       <c r="D15" t="s">
-        <v>2841</v>
+        <v>3338</v>
       </c>
       <c r="E15" t="s">
         <v>10</v>
@@ -11043,7 +11043,7 @@
         <v>66</v>
       </c>
       <c r="D22" t="s">
-        <v>2842</v>
+        <v>2841</v>
       </c>
       <c r="E22" t="s">
         <v>10</v>
@@ -11101,7 +11101,7 @@
         <v>72</v>
       </c>
       <c r="D24" t="s">
-        <v>2843</v>
+        <v>2842</v>
       </c>
       <c r="E24" t="s">
         <v>10</v>
@@ -11130,7 +11130,7 @@
         <v>74</v>
       </c>
       <c r="D25" t="s">
-        <v>2844</v>
+        <v>2843</v>
       </c>
       <c r="E25" t="s">
         <v>10</v>
@@ -11188,7 +11188,7 @@
         <v>79</v>
       </c>
       <c r="D27" t="s">
-        <v>2845</v>
+        <v>2844</v>
       </c>
       <c r="E27" t="s">
         <v>10</v>
@@ -11217,7 +11217,7 @@
         <v>81</v>
       </c>
       <c r="D28" t="s">
-        <v>2846</v>
+        <v>2845</v>
       </c>
       <c r="E28" t="s">
         <v>10</v>
@@ -11304,7 +11304,7 @@
         <v>89</v>
       </c>
       <c r="D31" t="s">
-        <v>2847</v>
+        <v>2846</v>
       </c>
       <c r="E31" t="s">
         <v>10</v>
@@ -11333,7 +11333,7 @@
         <v>91</v>
       </c>
       <c r="D32" t="s">
-        <v>2848</v>
+        <v>2847</v>
       </c>
       <c r="E32" t="s">
         <v>10</v>
@@ -11362,7 +11362,7 @@
         <v>93</v>
       </c>
       <c r="D33" t="s">
-        <v>2849</v>
+        <v>2848</v>
       </c>
       <c r="E33" t="s">
         <v>10</v>
@@ -11507,7 +11507,7 @@
         <v>107</v>
       </c>
       <c r="D38" t="s">
-        <v>2850</v>
+        <v>2849</v>
       </c>
       <c r="E38" t="s">
         <v>10</v>
@@ -11536,7 +11536,7 @@
         <v>109</v>
       </c>
       <c r="D39" t="s">
-        <v>2851</v>
+        <v>2850</v>
       </c>
       <c r="E39" t="s">
         <v>10</v>
@@ -11681,7 +11681,7 @@
         <v>123</v>
       </c>
       <c r="D44" t="s">
-        <v>2852</v>
+        <v>2851</v>
       </c>
       <c r="E44" t="s">
         <v>10</v>
@@ -11710,7 +11710,7 @@
         <v>125</v>
       </c>
       <c r="D45" t="s">
-        <v>2853</v>
+        <v>2852</v>
       </c>
       <c r="E45" t="s">
         <v>10</v>
@@ -11739,7 +11739,7 @@
         <v>127</v>
       </c>
       <c r="D46" t="s">
-        <v>2854</v>
+        <v>2853</v>
       </c>
       <c r="E46" t="s">
         <v>10</v>
@@ -11768,7 +11768,7 @@
         <v>129</v>
       </c>
       <c r="D47" t="s">
-        <v>2855</v>
+        <v>2854</v>
       </c>
       <c r="E47" t="s">
         <v>10</v>
@@ -11797,7 +11797,7 @@
         <v>131</v>
       </c>
       <c r="D48" t="s">
-        <v>2856</v>
+        <v>2855</v>
       </c>
       <c r="E48" t="s">
         <v>10</v>
@@ -11855,7 +11855,7 @@
         <v>136</v>
       </c>
       <c r="D50" t="s">
-        <v>2857</v>
+        <v>2856</v>
       </c>
       <c r="E50" t="s">
         <v>10</v>
@@ -11884,7 +11884,7 @@
         <v>138</v>
       </c>
       <c r="D51" t="s">
-        <v>2858</v>
+        <v>2857</v>
       </c>
       <c r="E51" t="s">
         <v>10</v>
@@ -12058,7 +12058,7 @@
         <v>155</v>
       </c>
       <c r="D57" t="s">
-        <v>2859</v>
+        <v>2858</v>
       </c>
       <c r="E57" t="s">
         <v>10</v>
@@ -12116,7 +12116,7 @@
         <v>160</v>
       </c>
       <c r="D59" t="s">
-        <v>2860</v>
+        <v>2859</v>
       </c>
       <c r="E59" t="s">
         <v>10</v>
@@ -12145,7 +12145,7 @@
         <v>162</v>
       </c>
       <c r="D60" t="s">
-        <v>2861</v>
+        <v>2860</v>
       </c>
       <c r="E60" t="s">
         <v>10</v>
@@ -12174,7 +12174,7 @@
         <v>164</v>
       </c>
       <c r="D61" t="s">
-        <v>2862</v>
+        <v>2861</v>
       </c>
       <c r="E61" t="s">
         <v>10</v>
@@ -12290,7 +12290,7 @@
         <v>175</v>
       </c>
       <c r="D65" t="s">
-        <v>2863</v>
+        <v>2862</v>
       </c>
       <c r="E65" t="s">
         <v>10</v>
@@ -12377,7 +12377,7 @@
         <v>183</v>
       </c>
       <c r="D68" t="s">
-        <v>2864</v>
+        <v>2863</v>
       </c>
       <c r="E68" t="s">
         <v>10</v>
@@ -12406,7 +12406,7 @@
         <v>185</v>
       </c>
       <c r="D69" t="s">
-        <v>2865</v>
+        <v>2864</v>
       </c>
       <c r="E69" t="s">
         <v>10</v>
@@ -12435,7 +12435,7 @@
         <v>187</v>
       </c>
       <c r="D70" t="s">
-        <v>2866</v>
+        <v>2865</v>
       </c>
       <c r="E70" t="s">
         <v>10</v>
@@ -12551,7 +12551,7 @@
         <v>198</v>
       </c>
       <c r="D74" t="s">
-        <v>2867</v>
+        <v>2866</v>
       </c>
       <c r="E74" t="s">
         <v>10</v>
@@ -12783,7 +12783,7 @@
         <v>221</v>
       </c>
       <c r="D82" t="s">
-        <v>2868</v>
+        <v>2867</v>
       </c>
       <c r="E82" t="s">
         <v>10</v>
@@ -12899,7 +12899,7 @@
         <v>232</v>
       </c>
       <c r="D86" t="s">
-        <v>2869</v>
+        <v>2868</v>
       </c>
       <c r="E86" t="s">
         <v>10</v>
@@ -12928,7 +12928,7 @@
         <v>234</v>
       </c>
       <c r="D87" t="s">
-        <v>2870</v>
+        <v>2869</v>
       </c>
       <c r="E87" t="s">
         <v>10</v>
@@ -12986,7 +12986,7 @@
         <v>239</v>
       </c>
       <c r="D89" t="s">
-        <v>2871</v>
+        <v>2870</v>
       </c>
       <c r="E89" t="s">
         <v>10</v>
@@ -13015,7 +13015,7 @@
         <v>241</v>
       </c>
       <c r="D90" t="s">
-        <v>2872</v>
+        <v>2871</v>
       </c>
       <c r="E90" t="s">
         <v>10</v>
@@ -13044,7 +13044,7 @@
         <v>243</v>
       </c>
       <c r="D91" t="s">
-        <v>2873</v>
+        <v>2872</v>
       </c>
       <c r="E91" t="s">
         <v>10</v>
@@ -13102,7 +13102,7 @@
         <v>248</v>
       </c>
       <c r="D93" t="s">
-        <v>2874</v>
+        <v>2873</v>
       </c>
       <c r="E93" t="s">
         <v>10</v>
@@ -13131,7 +13131,7 @@
         <v>250</v>
       </c>
       <c r="D94" t="s">
-        <v>2875</v>
+        <v>2874</v>
       </c>
       <c r="E94" t="s">
         <v>10</v>
@@ -13392,7 +13392,7 @@
         <v>276</v>
       </c>
       <c r="D103" t="s">
-        <v>2876</v>
+        <v>2875</v>
       </c>
       <c r="E103" t="s">
         <v>10</v>
@@ -13450,7 +13450,7 @@
         <v>281</v>
       </c>
       <c r="D105" t="s">
-        <v>2877</v>
+        <v>2876</v>
       </c>
       <c r="E105" t="s">
         <v>10</v>
@@ -13479,7 +13479,7 @@
         <v>283</v>
       </c>
       <c r="D106" t="s">
-        <v>2878</v>
+        <v>2877</v>
       </c>
       <c r="E106" t="s">
         <v>10</v>
@@ -13508,7 +13508,7 @@
         <v>285</v>
       </c>
       <c r="D107" t="s">
-        <v>2879</v>
+        <v>2878</v>
       </c>
       <c r="E107" t="s">
         <v>10</v>
@@ -13711,7 +13711,7 @@
         <v>305</v>
       </c>
       <c r="D114" t="s">
-        <v>2880</v>
+        <v>2879</v>
       </c>
       <c r="E114" t="s">
         <v>10</v>
@@ -13740,7 +13740,7 @@
         <v>307</v>
       </c>
       <c r="D115" t="s">
-        <v>2881</v>
+        <v>2880</v>
       </c>
       <c r="E115" t="s">
         <v>10</v>
@@ -13769,7 +13769,7 @@
         <v>309</v>
       </c>
       <c r="D116" t="s">
-        <v>2882</v>
+        <v>2881</v>
       </c>
       <c r="E116" t="s">
         <v>10</v>
@@ -13798,7 +13798,7 @@
         <v>311</v>
       </c>
       <c r="D117" t="s">
-        <v>2883</v>
+        <v>2882</v>
       </c>
       <c r="E117" t="s">
         <v>10</v>
@@ -13827,7 +13827,7 @@
         <v>313</v>
       </c>
       <c r="D118" t="s">
-        <v>2884</v>
+        <v>2883</v>
       </c>
       <c r="E118" t="s">
         <v>10</v>
@@ -14175,7 +14175,7 @@
         <v>348</v>
       </c>
       <c r="D130" t="s">
-        <v>2885</v>
+        <v>2884</v>
       </c>
       <c r="E130" t="s">
         <v>10</v>
@@ -14204,7 +14204,7 @@
         <v>350</v>
       </c>
       <c r="D131" t="s">
-        <v>2886</v>
+        <v>2885</v>
       </c>
       <c r="E131" t="s">
         <v>10</v>
@@ -14233,7 +14233,7 @@
         <v>352</v>
       </c>
       <c r="D132" t="s">
-        <v>2887</v>
+        <v>2886</v>
       </c>
       <c r="E132" t="s">
         <v>10</v>
@@ -14262,7 +14262,7 @@
         <v>354</v>
       </c>
       <c r="D133" t="s">
-        <v>2888</v>
+        <v>2887</v>
       </c>
       <c r="E133" t="s">
         <v>10</v>
@@ -14291,7 +14291,7 @@
         <v>356</v>
       </c>
       <c r="D134" t="s">
-        <v>2889</v>
+        <v>2888</v>
       </c>
       <c r="E134" t="s">
         <v>10</v>
@@ -14320,7 +14320,7 @@
         <v>358</v>
       </c>
       <c r="D135" t="s">
-        <v>2890</v>
+        <v>2889</v>
       </c>
       <c r="E135" t="s">
         <v>10</v>
@@ -14349,7 +14349,7 @@
         <v>360</v>
       </c>
       <c r="D136" t="s">
-        <v>2891</v>
+        <v>2890</v>
       </c>
       <c r="E136" t="s">
         <v>10</v>
@@ -14378,7 +14378,7 @@
         <v>362</v>
       </c>
       <c r="D137" t="s">
-        <v>2892</v>
+        <v>2891</v>
       </c>
       <c r="E137" t="s">
         <v>10</v>
@@ -14407,7 +14407,7 @@
         <v>364</v>
       </c>
       <c r="D138" t="s">
-        <v>2893</v>
+        <v>2892</v>
       </c>
       <c r="E138" t="s">
         <v>10</v>
@@ -14436,7 +14436,7 @@
         <v>366</v>
       </c>
       <c r="D139" t="s">
-        <v>2894</v>
+        <v>2893</v>
       </c>
       <c r="E139" t="s">
         <v>10</v>
@@ -14465,7 +14465,7 @@
         <v>368</v>
       </c>
       <c r="D140" t="s">
-        <v>2895</v>
+        <v>2894</v>
       </c>
       <c r="E140" t="s">
         <v>10</v>
@@ -14494,7 +14494,7 @@
         <v>370</v>
       </c>
       <c r="D141" t="s">
-        <v>2896</v>
+        <v>2895</v>
       </c>
       <c r="E141" t="s">
         <v>10</v>
@@ -14523,7 +14523,7 @@
         <v>372</v>
       </c>
       <c r="D142" t="s">
-        <v>2897</v>
+        <v>2896</v>
       </c>
       <c r="E142" t="s">
         <v>10</v>
@@ -14668,7 +14668,7 @@
         <v>386</v>
       </c>
       <c r="D147" t="s">
-        <v>2898</v>
+        <v>2897</v>
       </c>
       <c r="E147" t="s">
         <v>10</v>
@@ -14697,7 +14697,7 @@
         <v>388</v>
       </c>
       <c r="D148" t="s">
-        <v>2899</v>
+        <v>2898</v>
       </c>
       <c r="E148" t="s">
         <v>10</v>
@@ -14726,7 +14726,7 @@
         <v>390</v>
       </c>
       <c r="D149" t="s">
-        <v>2900</v>
+        <v>2899</v>
       </c>
       <c r="E149" t="s">
         <v>10</v>
@@ -14755,7 +14755,7 @@
         <v>392</v>
       </c>
       <c r="D150" t="s">
-        <v>2901</v>
+        <v>2900</v>
       </c>
       <c r="E150" t="s">
         <v>10</v>
@@ -14784,7 +14784,7 @@
         <v>394</v>
       </c>
       <c r="D151" t="s">
-        <v>2902</v>
+        <v>2901</v>
       </c>
       <c r="E151" t="s">
         <v>10</v>
@@ -14813,7 +14813,7 @@
         <v>396</v>
       </c>
       <c r="D152" t="s">
-        <v>2903</v>
+        <v>2902</v>
       </c>
       <c r="E152" t="s">
         <v>10</v>
@@ -14929,7 +14929,7 @@
         <v>407</v>
       </c>
       <c r="D156" t="s">
-        <v>2904</v>
+        <v>2903</v>
       </c>
       <c r="E156" t="s">
         <v>10</v>
@@ -15132,7 +15132,7 @@
         <v>427</v>
       </c>
       <c r="D163" t="s">
-        <v>2905</v>
+        <v>2904</v>
       </c>
       <c r="E163" t="s">
         <v>10</v>
@@ -15219,7 +15219,7 @@
         <v>435</v>
       </c>
       <c r="D166" t="s">
-        <v>2906</v>
+        <v>2905</v>
       </c>
       <c r="E166" t="s">
         <v>10</v>
@@ -15248,7 +15248,7 @@
         <v>437</v>
       </c>
       <c r="D167" t="s">
-        <v>2907</v>
+        <v>2906</v>
       </c>
       <c r="E167" t="s">
         <v>10</v>
@@ -15306,7 +15306,7 @@
         <v>442</v>
       </c>
       <c r="D169" t="s">
-        <v>2908</v>
+        <v>2907</v>
       </c>
       <c r="E169" t="s">
         <v>10</v>
@@ -15335,7 +15335,7 @@
         <v>444</v>
       </c>
       <c r="D170" t="s">
-        <v>2909</v>
+        <v>2908</v>
       </c>
       <c r="E170" t="s">
         <v>10</v>
@@ -15364,7 +15364,7 @@
         <v>446</v>
       </c>
       <c r="D171" t="s">
-        <v>2910</v>
+        <v>2909</v>
       </c>
       <c r="E171" t="s">
         <v>10</v>
@@ -15393,7 +15393,7 @@
         <v>448</v>
       </c>
       <c r="D172" t="s">
-        <v>2911</v>
+        <v>2910</v>
       </c>
       <c r="E172" t="s">
         <v>10</v>
@@ -15915,7 +15915,7 @@
         <v>501</v>
       </c>
       <c r="D190" t="s">
-        <v>2912</v>
+        <v>2911</v>
       </c>
       <c r="E190" t="s">
         <v>10</v>
@@ -15944,7 +15944,7 @@
         <v>503</v>
       </c>
       <c r="D191" t="s">
-        <v>2913</v>
+        <v>2912</v>
       </c>
       <c r="E191" t="s">
         <v>10</v>
@@ -15973,7 +15973,7 @@
         <v>505</v>
       </c>
       <c r="D192" t="s">
-        <v>2914</v>
+        <v>2913</v>
       </c>
       <c r="E192" t="s">
         <v>10</v>
@@ -16147,7 +16147,7 @@
         <v>522</v>
       </c>
       <c r="D198" t="s">
-        <v>2915</v>
+        <v>2914</v>
       </c>
       <c r="E198" t="s">
         <v>10</v>
@@ -16176,7 +16176,7 @@
         <v>524</v>
       </c>
       <c r="D199" t="s">
-        <v>2916</v>
+        <v>2915</v>
       </c>
       <c r="E199" t="s">
         <v>10</v>
@@ -16205,7 +16205,7 @@
         <v>526</v>
       </c>
       <c r="D200" t="s">
-        <v>2917</v>
+        <v>2916</v>
       </c>
       <c r="E200" t="s">
         <v>10</v>
@@ -16234,7 +16234,7 @@
         <v>528</v>
       </c>
       <c r="D201" t="s">
-        <v>2918</v>
+        <v>2917</v>
       </c>
       <c r="E201" t="s">
         <v>10</v>
@@ -16263,7 +16263,7 @@
         <v>530</v>
       </c>
       <c r="D202" t="s">
-        <v>2919</v>
+        <v>2918</v>
       </c>
       <c r="E202" t="s">
         <v>10</v>
@@ -16292,7 +16292,7 @@
         <v>532</v>
       </c>
       <c r="D203" t="s">
-        <v>2920</v>
+        <v>2919</v>
       </c>
       <c r="E203" t="s">
         <v>10</v>
@@ -16321,7 +16321,7 @@
         <v>534</v>
       </c>
       <c r="D204" t="s">
-        <v>2921</v>
+        <v>2920</v>
       </c>
       <c r="E204" t="s">
         <v>10</v>
@@ -16350,7 +16350,7 @@
         <v>536</v>
       </c>
       <c r="D205" t="s">
-        <v>2922</v>
+        <v>2921</v>
       </c>
       <c r="E205" t="s">
         <v>10</v>
@@ -16408,7 +16408,7 @@
         <v>541</v>
       </c>
       <c r="D207" t="s">
-        <v>2923</v>
+        <v>2922</v>
       </c>
       <c r="E207" t="s">
         <v>10</v>
@@ -16437,7 +16437,7 @@
         <v>543</v>
       </c>
       <c r="D208" t="s">
-        <v>2924</v>
+        <v>2923</v>
       </c>
       <c r="E208" t="s">
         <v>10</v>
@@ -16466,7 +16466,7 @@
         <v>545</v>
       </c>
       <c r="D209" t="s">
-        <v>2925</v>
+        <v>2924</v>
       </c>
       <c r="E209" t="s">
         <v>10</v>
@@ -16495,7 +16495,7 @@
         <v>547</v>
       </c>
       <c r="D210" t="s">
-        <v>2926</v>
+        <v>2925</v>
       </c>
       <c r="E210" t="s">
         <v>10</v>
@@ -16553,7 +16553,7 @@
         <v>552</v>
       </c>
       <c r="D212" t="s">
-        <v>2927</v>
+        <v>2926</v>
       </c>
       <c r="E212" t="s">
         <v>10</v>
@@ -16582,7 +16582,7 @@
         <v>554</v>
       </c>
       <c r="D213" t="s">
-        <v>2928</v>
+        <v>2927</v>
       </c>
       <c r="E213" t="s">
         <v>10</v>
@@ -16611,7 +16611,7 @@
         <v>556</v>
       </c>
       <c r="D214" t="s">
-        <v>2929</v>
+        <v>2928</v>
       </c>
       <c r="E214" t="s">
         <v>10</v>
@@ -16640,7 +16640,7 @@
         <v>558</v>
       </c>
       <c r="D215" t="s">
-        <v>2930</v>
+        <v>2929</v>
       </c>
       <c r="E215" t="s">
         <v>10</v>
@@ -16785,7 +16785,7 @@
         <v>572</v>
       </c>
       <c r="D220" t="s">
-        <v>2931</v>
+        <v>2930</v>
       </c>
       <c r="E220" t="s">
         <v>10</v>
@@ -16814,7 +16814,7 @@
         <v>574</v>
       </c>
       <c r="D221" t="s">
-        <v>2932</v>
+        <v>2931</v>
       </c>
       <c r="E221" t="s">
         <v>10</v>
@@ -16843,7 +16843,7 @@
         <v>576</v>
       </c>
       <c r="D222" t="s">
-        <v>2933</v>
+        <v>2932</v>
       </c>
       <c r="E222" t="s">
         <v>10</v>
@@ -17046,7 +17046,7 @@
         <v>596</v>
       </c>
       <c r="D229" t="s">
-        <v>2934</v>
+        <v>2933</v>
       </c>
       <c r="E229" t="s">
         <v>10</v>
@@ -17075,7 +17075,7 @@
         <v>598</v>
       </c>
       <c r="D230" t="s">
-        <v>2935</v>
+        <v>2934</v>
       </c>
       <c r="E230" t="s">
         <v>10</v>
@@ -17104,7 +17104,7 @@
         <v>600</v>
       </c>
       <c r="D231" t="s">
-        <v>2936</v>
+        <v>2935</v>
       </c>
       <c r="E231" t="s">
         <v>10</v>
@@ -17133,7 +17133,7 @@
         <v>602</v>
       </c>
       <c r="D232" t="s">
-        <v>2937</v>
+        <v>2936</v>
       </c>
       <c r="E232" t="s">
         <v>10</v>
@@ -17162,7 +17162,7 @@
         <v>604</v>
       </c>
       <c r="D233" t="s">
-        <v>2938</v>
+        <v>2937</v>
       </c>
       <c r="E233" t="s">
         <v>10</v>
@@ -17191,7 +17191,7 @@
         <v>606</v>
       </c>
       <c r="D234" t="s">
-        <v>2939</v>
+        <v>2938</v>
       </c>
       <c r="E234" t="s">
         <v>10</v>
@@ -17249,7 +17249,7 @@
         <v>611</v>
       </c>
       <c r="D236" t="s">
-        <v>2940</v>
+        <v>2939</v>
       </c>
       <c r="E236" t="s">
         <v>10</v>
@@ -17278,7 +17278,7 @@
         <v>613</v>
       </c>
       <c r="D237" t="s">
-        <v>2941</v>
+        <v>2940</v>
       </c>
       <c r="E237" t="s">
         <v>10</v>
@@ -17307,7 +17307,7 @@
         <v>615</v>
       </c>
       <c r="D238" t="s">
-        <v>2942</v>
+        <v>2941</v>
       </c>
       <c r="E238" t="s">
         <v>10</v>
@@ -17336,7 +17336,7 @@
         <v>617</v>
       </c>
       <c r="D239" t="s">
-        <v>2943</v>
+        <v>2942</v>
       </c>
       <c r="E239" t="s">
         <v>10</v>
@@ -17365,7 +17365,7 @@
         <v>619</v>
       </c>
       <c r="D240" t="s">
-        <v>2944</v>
+        <v>2943</v>
       </c>
       <c r="E240" t="s">
         <v>10</v>
@@ -17394,7 +17394,7 @@
         <v>621</v>
       </c>
       <c r="D241" t="s">
-        <v>2945</v>
+        <v>2944</v>
       </c>
       <c r="E241" t="s">
         <v>10</v>
@@ -17423,7 +17423,7 @@
         <v>623</v>
       </c>
       <c r="D242" t="s">
-        <v>2946</v>
+        <v>2945</v>
       </c>
       <c r="E242" t="s">
         <v>10</v>
@@ -17481,7 +17481,7 @@
         <v>628</v>
       </c>
       <c r="D244" t="s">
-        <v>2947</v>
+        <v>2946</v>
       </c>
       <c r="E244" t="s">
         <v>10</v>
@@ -17510,7 +17510,7 @@
         <v>630</v>
       </c>
       <c r="D245" t="s">
-        <v>2948</v>
+        <v>2947</v>
       </c>
       <c r="E245" t="s">
         <v>10</v>
@@ -17539,7 +17539,7 @@
         <v>632</v>
       </c>
       <c r="D246" t="s">
-        <v>2949</v>
+        <v>2948</v>
       </c>
       <c r="E246" t="s">
         <v>10</v>
@@ -17568,7 +17568,7 @@
         <v>634</v>
       </c>
       <c r="D247" t="s">
-        <v>2950</v>
+        <v>2949</v>
       </c>
       <c r="E247" t="s">
         <v>10</v>
@@ -17597,7 +17597,7 @@
         <v>636</v>
       </c>
       <c r="D248" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
       <c r="E248" t="s">
         <v>10</v>
@@ -17626,7 +17626,7 @@
         <v>638</v>
       </c>
       <c r="D249" t="s">
-        <v>2952</v>
+        <v>2951</v>
       </c>
       <c r="E249" t="s">
         <v>10</v>
@@ -17655,7 +17655,7 @@
         <v>640</v>
       </c>
       <c r="D250" t="s">
-        <v>2953</v>
+        <v>2952</v>
       </c>
       <c r="E250" t="s">
         <v>10</v>
@@ -17684,7 +17684,7 @@
         <v>642</v>
       </c>
       <c r="D251" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="E251" t="s">
         <v>10</v>
@@ -17800,7 +17800,7 @@
         <v>653</v>
       </c>
       <c r="D255" t="s">
-        <v>2955</v>
+        <v>2954</v>
       </c>
       <c r="E255" t="s">
         <v>10</v>
@@ -17829,7 +17829,7 @@
         <v>655</v>
       </c>
       <c r="D256" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="E256" t="s">
         <v>10</v>
@@ -17858,7 +17858,7 @@
         <v>657</v>
       </c>
       <c r="D257" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="E257" t="s">
         <v>10</v>
@@ -17887,7 +17887,7 @@
         <v>659</v>
       </c>
       <c r="D258" t="s">
-        <v>2958</v>
+        <v>2957</v>
       </c>
       <c r="E258" t="s">
         <v>10</v>
@@ -18090,7 +18090,7 @@
         <v>679</v>
       </c>
       <c r="D265" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="E265" t="s">
         <v>10</v>
@@ -18119,7 +18119,7 @@
         <v>681</v>
       </c>
       <c r="D266" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="E266" t="s">
         <v>10</v>
@@ -18148,7 +18148,7 @@
         <v>683</v>
       </c>
       <c r="D267" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="E267" t="s">
         <v>10</v>
@@ -18177,7 +18177,7 @@
         <v>685</v>
       </c>
       <c r="D268" t="s">
-        <v>2962</v>
+        <v>2961</v>
       </c>
       <c r="E268" t="s">
         <v>10</v>
@@ -18264,7 +18264,7 @@
         <v>693</v>
       </c>
       <c r="D271" t="s">
-        <v>2963</v>
+        <v>2962</v>
       </c>
       <c r="E271" t="s">
         <v>10</v>
@@ -18293,7 +18293,7 @@
         <v>695</v>
       </c>
       <c r="D272" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="E272" t="s">
         <v>10</v>
@@ -18351,7 +18351,7 @@
         <v>700</v>
       </c>
       <c r="D274" t="s">
-        <v>2965</v>
+        <v>2964</v>
       </c>
       <c r="E274" t="s">
         <v>10</v>
@@ -18380,7 +18380,7 @@
         <v>702</v>
       </c>
       <c r="D275" t="s">
-        <v>2966</v>
+        <v>2965</v>
       </c>
       <c r="E275" t="s">
         <v>10</v>
@@ -18409,7 +18409,7 @@
         <v>704</v>
       </c>
       <c r="D276" t="s">
-        <v>2967</v>
+        <v>2966</v>
       </c>
       <c r="E276" t="s">
         <v>10</v>
@@ -18438,7 +18438,7 @@
         <v>706</v>
       </c>
       <c r="D277" t="s">
-        <v>2968</v>
+        <v>2967</v>
       </c>
       <c r="E277" t="s">
         <v>10</v>
@@ -18612,7 +18612,7 @@
         <v>723</v>
       </c>
       <c r="D283" t="s">
-        <v>2969</v>
+        <v>2968</v>
       </c>
       <c r="E283" t="s">
         <v>10</v>
@@ -18989,7 +18989,7 @@
         <v>761</v>
       </c>
       <c r="D296" t="s">
-        <v>2970</v>
+        <v>2969</v>
       </c>
       <c r="E296" t="s">
         <v>10</v>
@@ -19018,7 +19018,7 @@
         <v>763</v>
       </c>
       <c r="D297" t="s">
-        <v>2971</v>
+        <v>2970</v>
       </c>
       <c r="E297" t="s">
         <v>10</v>
@@ -19047,7 +19047,7 @@
         <v>765</v>
       </c>
       <c r="D298" t="s">
-        <v>2972</v>
+        <v>2971</v>
       </c>
       <c r="E298" t="s">
         <v>10</v>
@@ -19076,7 +19076,7 @@
         <v>767</v>
       </c>
       <c r="D299" t="s">
-        <v>2973</v>
+        <v>2972</v>
       </c>
       <c r="E299" t="s">
         <v>10</v>
@@ -19105,7 +19105,7 @@
         <v>769</v>
       </c>
       <c r="D300" t="s">
-        <v>2974</v>
+        <v>2973</v>
       </c>
       <c r="E300" t="s">
         <v>10</v>
@@ -19163,7 +19163,7 @@
         <v>774</v>
       </c>
       <c r="D302" t="s">
-        <v>2975</v>
+        <v>2974</v>
       </c>
       <c r="E302" t="s">
         <v>10</v>
@@ -19192,7 +19192,7 @@
         <v>776</v>
       </c>
       <c r="D303" t="s">
-        <v>2976</v>
+        <v>2975</v>
       </c>
       <c r="E303" t="s">
         <v>10</v>
@@ -19221,7 +19221,7 @@
         <v>778</v>
       </c>
       <c r="D304" t="s">
-        <v>2977</v>
+        <v>2976</v>
       </c>
       <c r="E304" t="s">
         <v>10</v>
@@ -19250,7 +19250,7 @@
         <v>780</v>
       </c>
       <c r="D305" t="s">
-        <v>2978</v>
+        <v>2977</v>
       </c>
       <c r="E305" t="s">
         <v>10</v>
@@ -19279,7 +19279,7 @@
         <v>782</v>
       </c>
       <c r="D306" t="s">
-        <v>2979</v>
+        <v>2978</v>
       </c>
       <c r="E306" t="s">
         <v>10</v>
@@ -19366,7 +19366,7 @@
         <v>790</v>
       </c>
       <c r="D309" t="s">
-        <v>2980</v>
+        <v>2979</v>
       </c>
       <c r="E309" t="s">
         <v>10</v>
@@ -19395,7 +19395,7 @@
         <v>792</v>
       </c>
       <c r="D310" t="s">
-        <v>2981</v>
+        <v>2980</v>
       </c>
       <c r="E310" t="s">
         <v>10</v>
@@ -19424,7 +19424,7 @@
         <v>794</v>
       </c>
       <c r="D311" t="s">
-        <v>2982</v>
+        <v>2981</v>
       </c>
       <c r="E311" t="s">
         <v>10</v>
@@ -19453,7 +19453,7 @@
         <v>796</v>
       </c>
       <c r="D312" t="s">
-        <v>2983</v>
+        <v>2982</v>
       </c>
       <c r="E312" t="s">
         <v>10</v>
@@ -19482,7 +19482,7 @@
         <v>798</v>
       </c>
       <c r="D313" t="s">
-        <v>2984</v>
+        <v>2983</v>
       </c>
       <c r="E313" t="s">
         <v>10</v>
@@ -19511,7 +19511,7 @@
         <v>800</v>
       </c>
       <c r="D314" t="s">
-        <v>2985</v>
+        <v>2984</v>
       </c>
       <c r="E314" t="s">
         <v>10</v>
@@ -19540,7 +19540,7 @@
         <v>802</v>
       </c>
       <c r="D315" t="s">
-        <v>2986</v>
+        <v>2985</v>
       </c>
       <c r="E315" t="s">
         <v>10</v>
@@ -19569,7 +19569,7 @@
         <v>804</v>
       </c>
       <c r="D316" t="s">
-        <v>2987</v>
+        <v>2986</v>
       </c>
       <c r="E316" t="s">
         <v>10</v>
@@ -19598,7 +19598,7 @@
         <v>806</v>
       </c>
       <c r="D317" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
       <c r="E317" t="s">
         <v>10</v>
@@ -19627,7 +19627,7 @@
         <v>808</v>
       </c>
       <c r="D318" t="s">
-        <v>2989</v>
+        <v>2988</v>
       </c>
       <c r="E318" t="s">
         <v>10</v>
@@ -19656,7 +19656,7 @@
         <v>810</v>
       </c>
       <c r="D319" t="s">
-        <v>2990</v>
+        <v>2989</v>
       </c>
       <c r="E319" t="s">
         <v>10</v>
@@ -19685,7 +19685,7 @@
         <v>812</v>
       </c>
       <c r="D320" t="s">
-        <v>2991</v>
+        <v>2990</v>
       </c>
       <c r="E320" t="s">
         <v>10</v>
@@ -19801,7 +19801,7 @@
         <v>823</v>
       </c>
       <c r="D324" t="s">
-        <v>2992</v>
+        <v>2991</v>
       </c>
       <c r="E324" t="s">
         <v>10</v>
@@ -19917,7 +19917,7 @@
         <v>834</v>
       </c>
       <c r="D328" t="s">
-        <v>2993</v>
+        <v>2992</v>
       </c>
       <c r="E328" t="s">
         <v>10</v>
@@ -19946,7 +19946,7 @@
         <v>836</v>
       </c>
       <c r="D329" t="s">
-        <v>2994</v>
+        <v>2993</v>
       </c>
       <c r="E329" t="s">
         <v>10</v>
@@ -19975,7 +19975,7 @@
         <v>838</v>
       </c>
       <c r="D330" t="s">
-        <v>2995</v>
+        <v>2994</v>
       </c>
       <c r="E330" t="s">
         <v>10</v>
@@ -20033,7 +20033,7 @@
         <v>843</v>
       </c>
       <c r="D332" t="s">
-        <v>2996</v>
+        <v>2995</v>
       </c>
       <c r="E332" t="s">
         <v>10</v>
@@ -20265,7 +20265,7 @@
         <v>866</v>
       </c>
       <c r="D340" t="s">
-        <v>2997</v>
+        <v>2996</v>
       </c>
       <c r="E340" t="s">
         <v>10</v>
@@ -20294,7 +20294,7 @@
         <v>868</v>
       </c>
       <c r="D341" t="s">
-        <v>2998</v>
+        <v>2997</v>
       </c>
       <c r="E341" t="s">
         <v>10</v>
@@ -20323,7 +20323,7 @@
         <v>870</v>
       </c>
       <c r="D342" t="s">
-        <v>2999</v>
+        <v>2998</v>
       </c>
       <c r="E342" t="s">
         <v>10</v>
@@ -20352,7 +20352,7 @@
         <v>872</v>
       </c>
       <c r="D343" t="s">
-        <v>3000</v>
+        <v>2999</v>
       </c>
       <c r="E343" t="s">
         <v>10</v>
@@ -20381,7 +20381,7 @@
         <v>874</v>
       </c>
       <c r="D344" t="s">
-        <v>3001</v>
+        <v>3000</v>
       </c>
       <c r="E344" t="s">
         <v>10</v>
@@ -20468,7 +20468,7 @@
         <v>882</v>
       </c>
       <c r="D347" t="s">
-        <v>3002</v>
+        <v>3001</v>
       </c>
       <c r="E347" t="s">
         <v>10</v>
@@ -20497,7 +20497,7 @@
         <v>884</v>
       </c>
       <c r="D348" t="s">
-        <v>3003</v>
+        <v>3002</v>
       </c>
       <c r="E348" t="s">
         <v>10</v>
@@ -20526,7 +20526,7 @@
         <v>886</v>
       </c>
       <c r="D349" t="s">
-        <v>3004</v>
+        <v>3003</v>
       </c>
       <c r="E349" t="s">
         <v>10</v>
@@ -20555,7 +20555,7 @@
         <v>888</v>
       </c>
       <c r="D350" t="s">
-        <v>3005</v>
+        <v>3004</v>
       </c>
       <c r="E350" t="s">
         <v>10</v>
@@ -20584,7 +20584,7 @@
         <v>890</v>
       </c>
       <c r="D351" t="s">
-        <v>3006</v>
+        <v>3005</v>
       </c>
       <c r="E351" t="s">
         <v>10</v>
@@ -20700,7 +20700,7 @@
         <v>901</v>
       </c>
       <c r="D355" t="s">
-        <v>3007</v>
+        <v>3006</v>
       </c>
       <c r="E355" t="s">
         <v>10</v>
@@ -20729,7 +20729,7 @@
         <v>903</v>
       </c>
       <c r="D356" t="s">
-        <v>3008</v>
+        <v>3007</v>
       </c>
       <c r="E356" t="s">
         <v>10</v>
@@ -20758,7 +20758,7 @@
         <v>905</v>
       </c>
       <c r="D357" t="s">
-        <v>3009</v>
+        <v>3008</v>
       </c>
       <c r="E357" t="s">
         <v>10</v>
@@ -20787,7 +20787,7 @@
         <v>907</v>
       </c>
       <c r="D358" t="s">
-        <v>3010</v>
+        <v>3009</v>
       </c>
       <c r="E358" t="s">
         <v>10</v>
@@ -20932,7 +20932,7 @@
         <v>921</v>
       </c>
       <c r="D363" t="s">
-        <v>3011</v>
+        <v>3010</v>
       </c>
       <c r="E363" t="s">
         <v>10</v>
@@ -20961,7 +20961,7 @@
         <v>923</v>
       </c>
       <c r="D364" t="s">
-        <v>3012</v>
+        <v>3011</v>
       </c>
       <c r="E364" t="s">
         <v>10</v>
@@ -21019,7 +21019,7 @@
         <v>928</v>
       </c>
       <c r="D366" t="s">
-        <v>3013</v>
+        <v>3012</v>
       </c>
       <c r="E366" t="s">
         <v>10</v>
@@ -21309,7 +21309,7 @@
         <v>957</v>
       </c>
       <c r="D376" t="s">
-        <v>3014</v>
+        <v>3013</v>
       </c>
       <c r="E376" t="s">
         <v>10</v>
@@ -21512,7 +21512,7 @@
         <v>977</v>
       </c>
       <c r="D383" t="s">
-        <v>3015</v>
+        <v>3014</v>
       </c>
       <c r="E383" t="s">
         <v>10</v>
@@ -21541,7 +21541,7 @@
         <v>979</v>
       </c>
       <c r="D384" t="s">
-        <v>3016</v>
+        <v>3015</v>
       </c>
       <c r="E384" t="s">
         <v>10</v>
@@ -21570,7 +21570,7 @@
         <v>981</v>
       </c>
       <c r="D385" t="s">
-        <v>3017</v>
+        <v>3016</v>
       </c>
       <c r="E385" t="s">
         <v>10</v>
@@ -21599,7 +21599,7 @@
         <v>983</v>
       </c>
       <c r="D386" t="s">
-        <v>3018</v>
+        <v>3017</v>
       </c>
       <c r="E386" t="s">
         <v>10</v>
@@ -21628,7 +21628,7 @@
         <v>985</v>
       </c>
       <c r="D387" t="s">
-        <v>3019</v>
+        <v>3018</v>
       </c>
       <c r="E387" t="s">
         <v>10</v>
@@ -21802,7 +21802,7 @@
         <v>1002</v>
       </c>
       <c r="D393" t="s">
-        <v>3020</v>
+        <v>3019</v>
       </c>
       <c r="E393" t="s">
         <v>10</v>
@@ -21947,7 +21947,7 @@
         <v>1016</v>
       </c>
       <c r="D398" t="s">
-        <v>3021</v>
+        <v>3020</v>
       </c>
       <c r="E398" t="s">
         <v>10</v>
@@ -22150,7 +22150,7 @@
         <v>1036</v>
       </c>
       <c r="D405" t="s">
-        <v>3022</v>
+        <v>3021</v>
       </c>
       <c r="E405" t="s">
         <v>10</v>
@@ -22179,7 +22179,7 @@
         <v>1038</v>
       </c>
       <c r="D406" t="s">
-        <v>3023</v>
+        <v>3022</v>
       </c>
       <c r="E406" t="s">
         <v>10</v>
@@ -22208,7 +22208,7 @@
         <v>1040</v>
       </c>
       <c r="D407" t="s">
-        <v>3024</v>
+        <v>3023</v>
       </c>
       <c r="E407" t="s">
         <v>10</v>
@@ -22237,7 +22237,7 @@
         <v>1042</v>
       </c>
       <c r="D408" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="E408" t="s">
         <v>10</v>
@@ -22266,7 +22266,7 @@
         <v>1044</v>
       </c>
       <c r="D409" t="s">
-        <v>3026</v>
+        <v>3025</v>
       </c>
       <c r="E409" t="s">
         <v>10</v>
@@ -22585,7 +22585,7 @@
         <v>1076</v>
       </c>
       <c r="D420" t="s">
-        <v>3027</v>
+        <v>3026</v>
       </c>
       <c r="E420" t="s">
         <v>10</v>
@@ -22614,7 +22614,7 @@
         <v>1078</v>
       </c>
       <c r="D421" t="s">
-        <v>3028</v>
+        <v>3027</v>
       </c>
       <c r="E421" t="s">
         <v>10</v>
@@ -22643,7 +22643,7 @@
         <v>1080</v>
       </c>
       <c r="D422" t="s">
-        <v>3029</v>
+        <v>3028</v>
       </c>
       <c r="E422" t="s">
         <v>10</v>
@@ -22672,7 +22672,7 @@
         <v>1082</v>
       </c>
       <c r="D423" t="s">
-        <v>3030</v>
+        <v>3029</v>
       </c>
       <c r="E423" t="s">
         <v>10</v>
@@ -22701,7 +22701,7 @@
         <v>1084</v>
       </c>
       <c r="D424" t="s">
-        <v>3031</v>
+        <v>3030</v>
       </c>
       <c r="E424" t="s">
         <v>10</v>
@@ -22730,7 +22730,7 @@
         <v>1086</v>
       </c>
       <c r="D425" t="s">
-        <v>3032</v>
+        <v>3031</v>
       </c>
       <c r="E425" t="s">
         <v>10</v>
@@ -22759,7 +22759,7 @@
         <v>1088</v>
       </c>
       <c r="D426" t="s">
-        <v>3033</v>
+        <v>3032</v>
       </c>
       <c r="E426" t="s">
         <v>10</v>
@@ -23339,7 +23339,7 @@
         <v>1147</v>
       </c>
       <c r="D446" t="s">
-        <v>3034</v>
+        <v>3033</v>
       </c>
       <c r="E446" t="s">
         <v>10</v>
@@ -23368,7 +23368,7 @@
         <v>1149</v>
       </c>
       <c r="D447" t="s">
-        <v>3035</v>
+        <v>3034</v>
       </c>
       <c r="E447" t="s">
         <v>10</v>
@@ -23513,7 +23513,7 @@
         <v>1163</v>
       </c>
       <c r="D452" t="s">
-        <v>3036</v>
+        <v>3035</v>
       </c>
       <c r="E452" t="s">
         <v>10</v>
@@ -23542,7 +23542,7 @@
         <v>1165</v>
       </c>
       <c r="D453" t="s">
-        <v>3037</v>
+        <v>3036</v>
       </c>
       <c r="E453" t="s">
         <v>10</v>
@@ -23571,7 +23571,7 @@
         <v>1167</v>
       </c>
       <c r="D454" t="s">
-        <v>3038</v>
+        <v>3037</v>
       </c>
       <c r="E454" t="s">
         <v>10</v>
@@ -23600,7 +23600,7 @@
         <v>1169</v>
       </c>
       <c r="D455" t="s">
-        <v>3039</v>
+        <v>3038</v>
       </c>
       <c r="E455" t="s">
         <v>10</v>
@@ -23629,7 +23629,7 @@
         <v>1171</v>
       </c>
       <c r="D456" t="s">
-        <v>3040</v>
+        <v>3039</v>
       </c>
       <c r="E456" t="s">
         <v>10</v>
@@ -23658,7 +23658,7 @@
         <v>1173</v>
       </c>
       <c r="D457" t="s">
-        <v>3041</v>
+        <v>3040</v>
       </c>
       <c r="E457" t="s">
         <v>10</v>
@@ -23745,7 +23745,7 @@
         <v>1181</v>
       </c>
       <c r="D460" t="s">
-        <v>3042</v>
+        <v>3041</v>
       </c>
       <c r="E460" t="s">
         <v>10</v>
@@ -23774,7 +23774,7 @@
         <v>1183</v>
       </c>
       <c r="D461" t="s">
-        <v>3043</v>
+        <v>3042</v>
       </c>
       <c r="E461" t="s">
         <v>10</v>
@@ -23803,7 +23803,7 @@
         <v>1185</v>
       </c>
       <c r="D462" t="s">
-        <v>3044</v>
+        <v>3043</v>
       </c>
       <c r="E462" t="s">
         <v>10</v>
@@ -23832,7 +23832,7 @@
         <v>1187</v>
       </c>
       <c r="D463" t="s">
-        <v>3045</v>
+        <v>3044</v>
       </c>
       <c r="E463" t="s">
         <v>10</v>
@@ -23861,7 +23861,7 @@
         <v>1189</v>
       </c>
       <c r="D464" t="s">
-        <v>3046</v>
+        <v>3045</v>
       </c>
       <c r="E464" t="s">
         <v>10</v>
@@ -23890,7 +23890,7 @@
         <v>1191</v>
       </c>
       <c r="D465" t="s">
-        <v>3047</v>
+        <v>3046</v>
       </c>
       <c r="E465" t="s">
         <v>10</v>
@@ -23919,7 +23919,7 @@
         <v>1193</v>
       </c>
       <c r="D466" t="s">
-        <v>3048</v>
+        <v>3047</v>
       </c>
       <c r="E466" t="s">
         <v>10</v>
@@ -23948,7 +23948,7 @@
         <v>1195</v>
       </c>
       <c r="D467" t="s">
-        <v>3049</v>
+        <v>3048</v>
       </c>
       <c r="E467" t="s">
         <v>10</v>
@@ -23977,7 +23977,7 @@
         <v>1197</v>
       </c>
       <c r="D468" t="s">
-        <v>3050</v>
+        <v>3049</v>
       </c>
       <c r="E468" t="s">
         <v>10</v>
@@ -24209,7 +24209,7 @@
         <v>1220</v>
       </c>
       <c r="D476" t="s">
-        <v>3051</v>
+        <v>3050</v>
       </c>
       <c r="E476" t="s">
         <v>10</v>
@@ -24238,7 +24238,7 @@
         <v>1222</v>
       </c>
       <c r="D477" t="s">
-        <v>3052</v>
+        <v>3051</v>
       </c>
       <c r="E477" t="s">
         <v>10</v>
@@ -24267,7 +24267,7 @@
         <v>1224</v>
       </c>
       <c r="D478" t="s">
-        <v>3053</v>
+        <v>3052</v>
       </c>
       <c r="E478" t="s">
         <v>10</v>
@@ -24296,7 +24296,7 @@
         <v>1226</v>
       </c>
       <c r="D479" t="s">
-        <v>3054</v>
+        <v>3053</v>
       </c>
       <c r="E479" t="s">
         <v>10</v>
@@ -24325,7 +24325,7 @@
         <v>1228</v>
       </c>
       <c r="D480" t="s">
-        <v>3055</v>
+        <v>3054</v>
       </c>
       <c r="E480" t="s">
         <v>10</v>
@@ -24354,7 +24354,7 @@
         <v>1230</v>
       </c>
       <c r="D481" t="s">
-        <v>3056</v>
+        <v>3055</v>
       </c>
       <c r="E481" t="s">
         <v>10</v>
@@ -24383,7 +24383,7 @@
         <v>1232</v>
       </c>
       <c r="D482" t="s">
-        <v>3057</v>
+        <v>3056</v>
       </c>
       <c r="E482" t="s">
         <v>10</v>
@@ -24586,7 +24586,7 @@
         <v>1252</v>
       </c>
       <c r="D489" t="s">
-        <v>3058</v>
+        <v>3057</v>
       </c>
       <c r="E489" t="s">
         <v>10</v>
@@ -24789,7 +24789,7 @@
         <v>1272</v>
       </c>
       <c r="D496" t="s">
-        <v>3059</v>
+        <v>3058</v>
       </c>
       <c r="E496" t="s">
         <v>10</v>
@@ -24818,7 +24818,7 @@
         <v>1274</v>
       </c>
       <c r="D497" t="s">
-        <v>3060</v>
+        <v>3059</v>
       </c>
       <c r="E497" t="s">
         <v>10</v>
@@ -24847,7 +24847,7 @@
         <v>1276</v>
       </c>
       <c r="D498" t="s">
-        <v>3061</v>
+        <v>3060</v>
       </c>
       <c r="E498" t="s">
         <v>10</v>
@@ -24876,7 +24876,7 @@
         <v>1278</v>
       </c>
       <c r="D499" t="s">
-        <v>3062</v>
+        <v>3061</v>
       </c>
       <c r="E499" t="s">
         <v>10</v>
@@ -24905,7 +24905,7 @@
         <v>1280</v>
       </c>
       <c r="D500" t="s">
-        <v>3063</v>
+        <v>3062</v>
       </c>
       <c r="E500" t="s">
         <v>10</v>
@@ -24934,7 +24934,7 @@
         <v>1282</v>
       </c>
       <c r="D501" t="s">
-        <v>3064</v>
+        <v>3063</v>
       </c>
       <c r="E501" t="s">
         <v>10</v>
@@ -24992,7 +24992,7 @@
         <v>1287</v>
       </c>
       <c r="D503" t="s">
-        <v>3065</v>
+        <v>3064</v>
       </c>
       <c r="E503" t="s">
         <v>10</v>
@@ -25021,7 +25021,7 @@
         <v>1289</v>
       </c>
       <c r="D504" t="s">
-        <v>3066</v>
+        <v>3065</v>
       </c>
       <c r="E504" t="s">
         <v>10</v>
@@ -25050,7 +25050,7 @@
         <v>1291</v>
       </c>
       <c r="D505" t="s">
-        <v>3067</v>
+        <v>3066</v>
       </c>
       <c r="E505" t="s">
         <v>10</v>
@@ -25137,7 +25137,7 @@
         <v>1299</v>
       </c>
       <c r="D508" t="s">
-        <v>3068</v>
+        <v>3067</v>
       </c>
       <c r="E508" t="s">
         <v>10</v>
@@ -25166,7 +25166,7 @@
         <v>1301</v>
       </c>
       <c r="D509" t="s">
-        <v>3069</v>
+        <v>3068</v>
       </c>
       <c r="E509" t="s">
         <v>10</v>
@@ -25340,7 +25340,7 @@
         <v>1318</v>
       </c>
       <c r="D515" t="s">
-        <v>3070</v>
+        <v>3069</v>
       </c>
       <c r="E515" t="s">
         <v>10</v>
@@ -25369,7 +25369,7 @@
         <v>1320</v>
       </c>
       <c r="D516" t="s">
-        <v>3071</v>
+        <v>3070</v>
       </c>
       <c r="E516" t="s">
         <v>10</v>
@@ -25398,7 +25398,7 @@
         <v>1322</v>
       </c>
       <c r="D517" t="s">
-        <v>3072</v>
+        <v>3071</v>
       </c>
       <c r="E517" t="s">
         <v>10</v>
@@ -25456,7 +25456,7 @@
         <v>1327</v>
       </c>
       <c r="D519" t="s">
-        <v>3073</v>
+        <v>3072</v>
       </c>
       <c r="E519" t="s">
         <v>10</v>
@@ -25485,7 +25485,7 @@
         <v>1329</v>
       </c>
       <c r="D520" t="s">
-        <v>3074</v>
+        <v>3073</v>
       </c>
       <c r="E520" t="s">
         <v>10</v>
@@ -25514,7 +25514,7 @@
         <v>1331</v>
       </c>
       <c r="D521" t="s">
-        <v>3075</v>
+        <v>3074</v>
       </c>
       <c r="E521" t="s">
         <v>10</v>
@@ -25630,7 +25630,7 @@
         <v>1342</v>
       </c>
       <c r="D525" t="s">
-        <v>3076</v>
+        <v>3075</v>
       </c>
       <c r="E525" t="s">
         <v>10</v>
@@ -25659,7 +25659,7 @@
         <v>1344</v>
       </c>
       <c r="D526" t="s">
-        <v>3077</v>
+        <v>3076</v>
       </c>
       <c r="E526" t="s">
         <v>10</v>
@@ -25688,7 +25688,7 @@
         <v>1346</v>
       </c>
       <c r="D527" t="s">
-        <v>3078</v>
+        <v>3077</v>
       </c>
       <c r="E527" t="s">
         <v>10</v>
@@ -25717,7 +25717,7 @@
         <v>1348</v>
       </c>
       <c r="D528" t="s">
-        <v>3079</v>
+        <v>3078</v>
       </c>
       <c r="E528" t="s">
         <v>10</v>
@@ -25775,7 +25775,7 @@
         <v>1353</v>
       </c>
       <c r="D530" t="s">
-        <v>3080</v>
+        <v>3079</v>
       </c>
       <c r="E530" t="s">
         <v>10</v>
@@ -25804,7 +25804,7 @@
         <v>1355</v>
       </c>
       <c r="D531" t="s">
-        <v>3081</v>
+        <v>3080</v>
       </c>
       <c r="E531" t="s">
         <v>10</v>
@@ -25833,7 +25833,7 @@
         <v>1357</v>
       </c>
       <c r="D532" t="s">
-        <v>3082</v>
+        <v>3081</v>
       </c>
       <c r="E532" t="s">
         <v>10</v>
@@ -25862,7 +25862,7 @@
         <v>1359</v>
       </c>
       <c r="D533" t="s">
-        <v>3083</v>
+        <v>3082</v>
       </c>
       <c r="E533" t="s">
         <v>10</v>
@@ -25891,7 +25891,7 @@
         <v>1361</v>
       </c>
       <c r="D534" t="s">
-        <v>3084</v>
+        <v>3083</v>
       </c>
       <c r="E534" t="s">
         <v>10</v>
@@ -25920,7 +25920,7 @@
         <v>1363</v>
       </c>
       <c r="D535" t="s">
-        <v>3085</v>
+        <v>3084</v>
       </c>
       <c r="E535" t="s">
         <v>10</v>
@@ -26036,7 +26036,7 @@
         <v>1374</v>
       </c>
       <c r="D539" t="s">
-        <v>3086</v>
+        <v>3085</v>
       </c>
       <c r="E539" t="s">
         <v>10</v>
@@ -26065,7 +26065,7 @@
         <v>1376</v>
       </c>
       <c r="D540" t="s">
-        <v>3087</v>
+        <v>3086</v>
       </c>
       <c r="E540" t="s">
         <v>10</v>
@@ -26094,7 +26094,7 @@
         <v>1378</v>
       </c>
       <c r="D541" t="s">
-        <v>3088</v>
+        <v>3087</v>
       </c>
       <c r="E541" t="s">
         <v>10</v>
@@ -26152,7 +26152,7 @@
         <v>1383</v>
       </c>
       <c r="D543" t="s">
-        <v>3089</v>
+        <v>3088</v>
       </c>
       <c r="E543" t="s">
         <v>10</v>
@@ -26239,7 +26239,7 @@
         <v>1391</v>
       </c>
       <c r="D546" t="s">
-        <v>3090</v>
+        <v>3089</v>
       </c>
       <c r="E546" t="s">
         <v>10</v>
@@ -26268,7 +26268,7 @@
         <v>1393</v>
       </c>
       <c r="D547" t="s">
-        <v>3091</v>
+        <v>3090</v>
       </c>
       <c r="E547" t="s">
         <v>10</v>
@@ -26732,7 +26732,7 @@
         <v>1440</v>
       </c>
       <c r="D563" t="s">
-        <v>3092</v>
+        <v>3091</v>
       </c>
       <c r="E563" t="s">
         <v>10</v>
@@ -26761,7 +26761,7 @@
         <v>1442</v>
       </c>
       <c r="D564" t="s">
-        <v>3093</v>
+        <v>3092</v>
       </c>
       <c r="E564" t="s">
         <v>10</v>
@@ -26790,7 +26790,7 @@
         <v>1444</v>
       </c>
       <c r="D565" t="s">
-        <v>3094</v>
+        <v>3093</v>
       </c>
       <c r="E565" t="s">
         <v>10</v>
@@ -26819,7 +26819,7 @@
         <v>1446</v>
       </c>
       <c r="D566" t="s">
-        <v>3095</v>
+        <v>3094</v>
       </c>
       <c r="E566" t="s">
         <v>10</v>
@@ -26848,7 +26848,7 @@
         <v>1448</v>
       </c>
       <c r="D567" t="s">
-        <v>3096</v>
+        <v>3095</v>
       </c>
       <c r="E567" t="s">
         <v>10</v>
@@ -26877,7 +26877,7 @@
         <v>1450</v>
       </c>
       <c r="D568" t="s">
-        <v>3097</v>
+        <v>3096</v>
       </c>
       <c r="E568" t="s">
         <v>10</v>
@@ -26906,7 +26906,7 @@
         <v>1452</v>
       </c>
       <c r="D569" t="s">
-        <v>3098</v>
+        <v>3097</v>
       </c>
       <c r="E569" t="s">
         <v>10</v>
@@ -26964,7 +26964,7 @@
         <v>1457</v>
       </c>
       <c r="D571" t="s">
-        <v>3099</v>
+        <v>3098</v>
       </c>
       <c r="E571" t="s">
         <v>10</v>
@@ -26993,7 +26993,7 @@
         <v>1459</v>
       </c>
       <c r="D572" t="s">
-        <v>3100</v>
+        <v>3099</v>
       </c>
       <c r="E572" t="s">
         <v>10</v>
@@ -27167,7 +27167,7 @@
         <v>1476</v>
       </c>
       <c r="D578" t="s">
-        <v>3101</v>
+        <v>3100</v>
       </c>
       <c r="E578" t="s">
         <v>10</v>
@@ -27196,7 +27196,7 @@
         <v>1478</v>
       </c>
       <c r="D579" t="s">
-        <v>3102</v>
+        <v>3101</v>
       </c>
       <c r="E579" t="s">
         <v>10</v>
@@ -27283,7 +27283,7 @@
         <v>1486</v>
       </c>
       <c r="D582" t="s">
-        <v>3103</v>
+        <v>3102</v>
       </c>
       <c r="E582" t="s">
         <v>10</v>
@@ -27312,7 +27312,7 @@
         <v>1488</v>
       </c>
       <c r="D583" t="s">
-        <v>3104</v>
+        <v>3103</v>
       </c>
       <c r="E583" t="s">
         <v>10</v>
@@ -27341,7 +27341,7 @@
         <v>1490</v>
       </c>
       <c r="D584" t="s">
-        <v>3105</v>
+        <v>3104</v>
       </c>
       <c r="E584" t="s">
         <v>10</v>
@@ -27370,7 +27370,7 @@
         <v>1492</v>
       </c>
       <c r="D585" t="s">
-        <v>3106</v>
+        <v>3105</v>
       </c>
       <c r="E585" t="s">
         <v>10</v>
@@ -27399,7 +27399,7 @@
         <v>1494</v>
       </c>
       <c r="D586" t="s">
-        <v>3107</v>
+        <v>3106</v>
       </c>
       <c r="E586" t="s">
         <v>10</v>
@@ -27486,7 +27486,7 @@
         <v>1502</v>
       </c>
       <c r="D589" t="s">
-        <v>3108</v>
+        <v>3107</v>
       </c>
       <c r="E589" t="s">
         <v>10</v>
@@ -27515,7 +27515,7 @@
         <v>1504</v>
       </c>
       <c r="D590" t="s">
-        <v>3109</v>
+        <v>3108</v>
       </c>
       <c r="E590" t="s">
         <v>10</v>
@@ -27544,7 +27544,7 @@
         <v>1506</v>
       </c>
       <c r="D591" t="s">
-        <v>3110</v>
+        <v>3109</v>
       </c>
       <c r="E591" t="s">
         <v>10</v>
@@ -27573,7 +27573,7 @@
         <v>1508</v>
       </c>
       <c r="D592" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
       <c r="E592" t="s">
         <v>10</v>
@@ -27602,7 +27602,7 @@
         <v>1510</v>
       </c>
       <c r="D593" t="s">
-        <v>3112</v>
+        <v>3111</v>
       </c>
       <c r="E593" t="s">
         <v>10</v>
@@ -27631,7 +27631,7 @@
         <v>1512</v>
       </c>
       <c r="D594" t="s">
-        <v>3113</v>
+        <v>3112</v>
       </c>
       <c r="E594" t="s">
         <v>10</v>
@@ -27660,7 +27660,7 @@
         <v>1514</v>
       </c>
       <c r="D595" t="s">
-        <v>3114</v>
+        <v>3113</v>
       </c>
       <c r="E595" t="s">
         <v>10</v>
@@ -27689,7 +27689,7 @@
         <v>1516</v>
       </c>
       <c r="D596" t="s">
-        <v>3115</v>
+        <v>3114</v>
       </c>
       <c r="E596" t="s">
         <v>10</v>
@@ -27718,7 +27718,7 @@
         <v>1518</v>
       </c>
       <c r="D597" t="s">
-        <v>3116</v>
+        <v>3115</v>
       </c>
       <c r="E597" t="s">
         <v>10</v>
@@ -27747,7 +27747,7 @@
         <v>1520</v>
       </c>
       <c r="D598" t="s">
-        <v>3117</v>
+        <v>3116</v>
       </c>
       <c r="E598" t="s">
         <v>10</v>
@@ -27892,7 +27892,7 @@
         <v>1534</v>
       </c>
       <c r="D603" t="s">
-        <v>3118</v>
+        <v>3117</v>
       </c>
       <c r="E603" t="s">
         <v>10</v>
@@ -27921,7 +27921,7 @@
         <v>1536</v>
       </c>
       <c r="D604" t="s">
-        <v>3119</v>
+        <v>3118</v>
       </c>
       <c r="E604" t="s">
         <v>10</v>
@@ -28356,7 +28356,7 @@
         <v>1580</v>
       </c>
       <c r="D619" t="s">
-        <v>3120</v>
+        <v>3119</v>
       </c>
       <c r="E619" t="s">
         <v>10</v>
@@ -28385,7 +28385,7 @@
         <v>1582</v>
       </c>
       <c r="D620" t="s">
-        <v>3121</v>
+        <v>3120</v>
       </c>
       <c r="E620" t="s">
         <v>10</v>
@@ -28414,7 +28414,7 @@
         <v>1584</v>
       </c>
       <c r="D621" t="s">
-        <v>3122</v>
+        <v>3121</v>
       </c>
       <c r="E621" t="s">
         <v>10</v>
@@ -28443,7 +28443,7 @@
         <v>1586</v>
       </c>
       <c r="D622" t="s">
-        <v>3123</v>
+        <v>3122</v>
       </c>
       <c r="E622" t="s">
         <v>10</v>
@@ -28472,7 +28472,7 @@
         <v>1588</v>
       </c>
       <c r="D623" t="s">
-        <v>3124</v>
+        <v>3123</v>
       </c>
       <c r="E623" t="s">
         <v>10</v>
@@ -28501,7 +28501,7 @@
         <v>1590</v>
       </c>
       <c r="D624" t="s">
-        <v>3125</v>
+        <v>3124</v>
       </c>
       <c r="E624" t="s">
         <v>10</v>
@@ -28530,7 +28530,7 @@
         <v>1592</v>
       </c>
       <c r="D625" t="s">
-        <v>3126</v>
+        <v>3125</v>
       </c>
       <c r="E625" t="s">
         <v>10</v>
@@ -28559,7 +28559,7 @@
         <v>1594</v>
       </c>
       <c r="D626" t="s">
-        <v>3127</v>
+        <v>3126</v>
       </c>
       <c r="E626" t="s">
         <v>10</v>
@@ -28588,7 +28588,7 @@
         <v>1596</v>
       </c>
       <c r="D627" t="s">
-        <v>3128</v>
+        <v>3127</v>
       </c>
       <c r="E627" t="s">
         <v>10</v>
@@ -28704,7 +28704,7 @@
         <v>1607</v>
       </c>
       <c r="D631" t="s">
-        <v>3129</v>
+        <v>3128</v>
       </c>
       <c r="E631" t="s">
         <v>10</v>
@@ -28849,7 +28849,7 @@
         <v>1621</v>
       </c>
       <c r="D636" t="s">
-        <v>3130</v>
+        <v>3129</v>
       </c>
       <c r="E636" t="s">
         <v>10</v>
@@ -28878,7 +28878,7 @@
         <v>1623</v>
       </c>
       <c r="D637" t="s">
-        <v>3131</v>
+        <v>3130</v>
       </c>
       <c r="E637" t="s">
         <v>10</v>
@@ -28907,7 +28907,7 @@
         <v>1625</v>
       </c>
       <c r="D638" t="s">
-        <v>3132</v>
+        <v>3131</v>
       </c>
       <c r="E638" t="s">
         <v>10</v>
@@ -29168,7 +29168,7 @@
         <v>1651</v>
       </c>
       <c r="D647" t="s">
-        <v>3133</v>
+        <v>3132</v>
       </c>
       <c r="E647" t="s">
         <v>10</v>
@@ -29226,7 +29226,7 @@
         <v>1656</v>
       </c>
       <c r="D649" t="s">
-        <v>3134</v>
+        <v>3133</v>
       </c>
       <c r="E649" t="s">
         <v>10</v>
@@ -29690,7 +29690,7 @@
         <v>1703</v>
       </c>
       <c r="D665" t="s">
-        <v>3135</v>
+        <v>3134</v>
       </c>
       <c r="E665" t="s">
         <v>10</v>
@@ -29951,7 +29951,7 @@
         <v>1729</v>
       </c>
       <c r="D674" t="s">
-        <v>3136</v>
+        <v>3135</v>
       </c>
       <c r="E674" t="s">
         <v>10</v>
@@ -30038,7 +30038,7 @@
         <v>1737</v>
       </c>
       <c r="D677" t="s">
-        <v>3137</v>
+        <v>3136</v>
       </c>
       <c r="E677" t="s">
         <v>10</v>
@@ -30067,7 +30067,7 @@
         <v>1739</v>
       </c>
       <c r="D678" t="s">
-        <v>3138</v>
+        <v>3137</v>
       </c>
       <c r="E678" t="s">
         <v>10</v>
@@ -30270,7 +30270,7 @@
         <v>1759</v>
       </c>
       <c r="D685" t="s">
-        <v>3139</v>
+        <v>3138</v>
       </c>
       <c r="E685" t="s">
         <v>10</v>
@@ -30299,7 +30299,7 @@
         <v>1761</v>
       </c>
       <c r="D686" t="s">
-        <v>3140</v>
+        <v>3139</v>
       </c>
       <c r="E686" t="s">
         <v>10</v>
@@ -30328,7 +30328,7 @@
         <v>1763</v>
       </c>
       <c r="D687" t="s">
-        <v>3141</v>
+        <v>3140</v>
       </c>
       <c r="E687" t="s">
         <v>10</v>
@@ -30357,7 +30357,7 @@
         <v>1765</v>
       </c>
       <c r="D688" t="s">
-        <v>3142</v>
+        <v>3141</v>
       </c>
       <c r="E688" t="s">
         <v>10</v>
@@ -30386,7 +30386,7 @@
         <v>1767</v>
       </c>
       <c r="D689" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
       <c r="E689" t="s">
         <v>10</v>
@@ -30415,7 +30415,7 @@
         <v>1769</v>
       </c>
       <c r="D690" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="E690" t="s">
         <v>10</v>
@@ -30444,7 +30444,7 @@
         <v>1771</v>
       </c>
       <c r="D691" t="s">
-        <v>3145</v>
+        <v>3144</v>
       </c>
       <c r="E691" t="s">
         <v>10</v>
@@ -30473,7 +30473,7 @@
         <v>1773</v>
       </c>
       <c r="D692" t="s">
-        <v>3146</v>
+        <v>3145</v>
       </c>
       <c r="E692" t="s">
         <v>10</v>
@@ -30502,7 +30502,7 @@
         <v>1775</v>
       </c>
       <c r="D693" t="s">
-        <v>3147</v>
+        <v>3146</v>
       </c>
       <c r="E693" t="s">
         <v>10</v>
@@ -30531,7 +30531,7 @@
         <v>1777</v>
       </c>
       <c r="D694" t="s">
-        <v>3148</v>
+        <v>3147</v>
       </c>
       <c r="E694" t="s">
         <v>10</v>
@@ -30560,7 +30560,7 @@
         <v>1779</v>
       </c>
       <c r="D695" t="s">
-        <v>3149</v>
+        <v>3148</v>
       </c>
       <c r="E695" t="s">
         <v>10</v>
@@ -30589,7 +30589,7 @@
         <v>1781</v>
       </c>
       <c r="D696" t="s">
-        <v>3150</v>
+        <v>3149</v>
       </c>
       <c r="E696" t="s">
         <v>10</v>
@@ -30763,7 +30763,7 @@
         <v>1798</v>
       </c>
       <c r="D702" t="s">
-        <v>3151</v>
+        <v>3150</v>
       </c>
       <c r="E702" t="s">
         <v>10</v>
@@ -30792,7 +30792,7 @@
         <v>1800</v>
       </c>
       <c r="D703" t="s">
-        <v>3152</v>
+        <v>3151</v>
       </c>
       <c r="E703" t="s">
         <v>10</v>
@@ -30821,7 +30821,7 @@
         <v>1802</v>
       </c>
       <c r="D704" t="s">
-        <v>3153</v>
+        <v>3152</v>
       </c>
       <c r="E704" t="s">
         <v>10</v>
@@ -30850,7 +30850,7 @@
         <v>1804</v>
       </c>
       <c r="D705" t="s">
-        <v>3154</v>
+        <v>3153</v>
       </c>
       <c r="E705" t="s">
         <v>10</v>
@@ -30879,7 +30879,7 @@
         <v>1806</v>
       </c>
       <c r="D706" t="s">
-        <v>3155</v>
+        <v>3154</v>
       </c>
       <c r="E706" t="s">
         <v>10</v>
@@ -30908,7 +30908,7 @@
         <v>1808</v>
       </c>
       <c r="D707" t="s">
-        <v>3156</v>
+        <v>3155</v>
       </c>
       <c r="E707" t="s">
         <v>10</v>
@@ -30937,7 +30937,7 @@
         <v>1810</v>
       </c>
       <c r="D708" t="s">
-        <v>3157</v>
+        <v>3156</v>
       </c>
       <c r="E708" t="s">
         <v>10</v>
@@ -30966,7 +30966,7 @@
         <v>1812</v>
       </c>
       <c r="D709" t="s">
-        <v>3158</v>
+        <v>3157</v>
       </c>
       <c r="E709" t="s">
         <v>10</v>
@@ -30995,7 +30995,7 @@
         <v>1814</v>
       </c>
       <c r="D710" t="s">
-        <v>3159</v>
+        <v>3158</v>
       </c>
       <c r="E710" t="s">
         <v>10</v>
@@ -31024,7 +31024,7 @@
         <v>1816</v>
       </c>
       <c r="D711" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
       <c r="E711" t="s">
         <v>10</v>
@@ -31053,7 +31053,7 @@
         <v>1818</v>
       </c>
       <c r="D712" t="s">
-        <v>3161</v>
+        <v>3160</v>
       </c>
       <c r="E712" t="s">
         <v>10</v>
@@ -31082,7 +31082,7 @@
         <v>1820</v>
       </c>
       <c r="D713" t="s">
-        <v>3162</v>
+        <v>3161</v>
       </c>
       <c r="E713" t="s">
         <v>10</v>
@@ -31140,7 +31140,7 @@
         <v>1825</v>
       </c>
       <c r="D715" t="s">
-        <v>3163</v>
+        <v>3162</v>
       </c>
       <c r="E715" t="s">
         <v>10</v>
@@ -31169,7 +31169,7 @@
         <v>1827</v>
       </c>
       <c r="D716" t="s">
-        <v>3164</v>
+        <v>3163</v>
       </c>
       <c r="E716" t="s">
         <v>10</v>
@@ -31198,7 +31198,7 @@
         <v>1829</v>
       </c>
       <c r="D717" t="s">
-        <v>3165</v>
+        <v>3164</v>
       </c>
       <c r="E717" t="s">
         <v>10</v>
@@ -31227,7 +31227,7 @@
         <v>1831</v>
       </c>
       <c r="D718" t="s">
-        <v>3166</v>
+        <v>3165</v>
       </c>
       <c r="E718" t="s">
         <v>10</v>
@@ -31285,7 +31285,7 @@
         <v>1836</v>
       </c>
       <c r="D720" t="s">
-        <v>3167</v>
+        <v>3166</v>
       </c>
       <c r="E720" t="s">
         <v>10</v>
@@ -31575,7 +31575,7 @@
         <v>1865</v>
       </c>
       <c r="D730" t="s">
-        <v>3168</v>
+        <v>3167</v>
       </c>
       <c r="E730" t="s">
         <v>10</v>
@@ -31604,7 +31604,7 @@
         <v>1867</v>
       </c>
       <c r="D731" t="s">
-        <v>3169</v>
+        <v>3168</v>
       </c>
       <c r="E731" t="s">
         <v>10</v>
@@ -31633,7 +31633,7 @@
         <v>1869</v>
       </c>
       <c r="D732" t="s">
-        <v>3170</v>
+        <v>3169</v>
       </c>
       <c r="E732" t="s">
         <v>10</v>
@@ -31662,7 +31662,7 @@
         <v>1871</v>
       </c>
       <c r="D733" t="s">
-        <v>3171</v>
+        <v>3170</v>
       </c>
       <c r="E733" t="s">
         <v>10</v>
@@ -31691,7 +31691,7 @@
         <v>1873</v>
       </c>
       <c r="D734" t="s">
-        <v>3172</v>
+        <v>3171</v>
       </c>
       <c r="E734" t="s">
         <v>10</v>
@@ -31720,7 +31720,7 @@
         <v>1875</v>
       </c>
       <c r="D735" t="s">
-        <v>3173</v>
+        <v>3172</v>
       </c>
       <c r="E735" t="s">
         <v>10</v>
@@ -31894,7 +31894,7 @@
         <v>1892</v>
       </c>
       <c r="D741" t="s">
-        <v>3174</v>
+        <v>3173</v>
       </c>
       <c r="E741" t="s">
         <v>10</v>
@@ -31923,7 +31923,7 @@
         <v>1894</v>
       </c>
       <c r="D742" t="s">
-        <v>3175</v>
+        <v>3174</v>
       </c>
       <c r="E742" t="s">
         <v>10</v>
@@ -32010,7 +32010,7 @@
         <v>1902</v>
       </c>
       <c r="D745" t="s">
-        <v>3176</v>
+        <v>3175</v>
       </c>
       <c r="E745" t="s">
         <v>10</v>
@@ -32039,7 +32039,7 @@
         <v>1904</v>
       </c>
       <c r="D746" t="s">
-        <v>3177</v>
+        <v>3176</v>
       </c>
       <c r="E746" t="s">
         <v>10</v>
@@ -32068,7 +32068,7 @@
         <v>1906</v>
       </c>
       <c r="D747" t="s">
-        <v>3178</v>
+        <v>3177</v>
       </c>
       <c r="E747" t="s">
         <v>10</v>
@@ -32097,7 +32097,7 @@
         <v>1908</v>
       </c>
       <c r="D748" t="s">
-        <v>3179</v>
+        <v>3178</v>
       </c>
       <c r="E748" t="s">
         <v>10</v>
@@ -32126,7 +32126,7 @@
         <v>1910</v>
       </c>
       <c r="D749" t="s">
-        <v>3180</v>
+        <v>3179</v>
       </c>
       <c r="E749" t="s">
         <v>10</v>
@@ -32155,7 +32155,7 @@
         <v>1912</v>
       </c>
       <c r="D750" t="s">
-        <v>3181</v>
+        <v>3180</v>
       </c>
       <c r="E750" t="s">
         <v>10</v>
@@ -32271,7 +32271,7 @@
         <v>1923</v>
       </c>
       <c r="D754" t="s">
-        <v>3182</v>
+        <v>3181</v>
       </c>
       <c r="E754" t="s">
         <v>10</v>
@@ -32300,7 +32300,7 @@
         <v>1925</v>
       </c>
       <c r="D755" t="s">
-        <v>3183</v>
+        <v>3182</v>
       </c>
       <c r="E755" t="s">
         <v>10</v>
@@ -32329,7 +32329,7 @@
         <v>1927</v>
       </c>
       <c r="D756" t="s">
-        <v>3184</v>
+        <v>3183</v>
       </c>
       <c r="E756" t="s">
         <v>10</v>
@@ -32358,7 +32358,7 @@
         <v>1929</v>
       </c>
       <c r="D757" t="s">
-        <v>3185</v>
+        <v>3184</v>
       </c>
       <c r="E757" t="s">
         <v>10</v>
@@ -32387,7 +32387,7 @@
         <v>1931</v>
       </c>
       <c r="D758" t="s">
-        <v>3186</v>
+        <v>3185</v>
       </c>
       <c r="E758" t="s">
         <v>10</v>
@@ -32416,7 +32416,7 @@
         <v>1933</v>
       </c>
       <c r="D759" t="s">
-        <v>3187</v>
+        <v>3186</v>
       </c>
       <c r="E759" t="s">
         <v>10</v>
@@ -32445,7 +32445,7 @@
         <v>1935</v>
       </c>
       <c r="D760" t="s">
-        <v>3188</v>
+        <v>3187</v>
       </c>
       <c r="E760" t="s">
         <v>10</v>
@@ -32474,7 +32474,7 @@
         <v>1937</v>
       </c>
       <c r="D761" t="s">
-        <v>3189</v>
+        <v>3188</v>
       </c>
       <c r="E761" t="s">
         <v>10</v>
@@ -32619,7 +32619,7 @@
         <v>1951</v>
       </c>
       <c r="D766" t="s">
-        <v>3190</v>
+        <v>3189</v>
       </c>
       <c r="E766" t="s">
         <v>10</v>
@@ -32822,7 +32822,7 @@
         <v>1971</v>
       </c>
       <c r="D773" t="s">
-        <v>3191</v>
+        <v>3190</v>
       </c>
       <c r="E773" t="s">
         <v>10</v>
@@ -32938,7 +32938,7 @@
         <v>1982</v>
       </c>
       <c r="D777" t="s">
-        <v>3192</v>
+        <v>3191</v>
       </c>
       <c r="E777" t="s">
         <v>10</v>
@@ -33054,7 +33054,7 @@
         <v>1993</v>
       </c>
       <c r="D781" t="s">
-        <v>3193</v>
+        <v>3192</v>
       </c>
       <c r="E781" t="s">
         <v>10</v>
@@ -33083,7 +33083,7 @@
         <v>1995</v>
       </c>
       <c r="D782" t="s">
-        <v>3194</v>
+        <v>3193</v>
       </c>
       <c r="E782" t="s">
         <v>10</v>
@@ -33112,7 +33112,7 @@
         <v>1997</v>
       </c>
       <c r="D783" t="s">
-        <v>3195</v>
+        <v>3194</v>
       </c>
       <c r="E783" t="s">
         <v>10</v>
@@ -33170,7 +33170,7 @@
         <v>2002</v>
       </c>
       <c r="D785" t="s">
-        <v>3196</v>
+        <v>3195</v>
       </c>
       <c r="E785" t="s">
         <v>10</v>
@@ -33199,7 +33199,7 @@
         <v>2004</v>
       </c>
       <c r="D786" t="s">
-        <v>3197</v>
+        <v>3196</v>
       </c>
       <c r="E786" t="s">
         <v>10</v>
@@ -33228,7 +33228,7 @@
         <v>2006</v>
       </c>
       <c r="D787" t="s">
-        <v>3198</v>
+        <v>3197</v>
       </c>
       <c r="E787" t="s">
         <v>10</v>
@@ -33286,7 +33286,7 @@
         <v>2011</v>
       </c>
       <c r="D789" t="s">
-        <v>3199</v>
+        <v>3198</v>
       </c>
       <c r="E789" t="s">
         <v>10</v>
@@ -33315,7 +33315,7 @@
         <v>2013</v>
       </c>
       <c r="D790" t="s">
-        <v>3200</v>
+        <v>3199</v>
       </c>
       <c r="E790" t="s">
         <v>10</v>
@@ -33344,7 +33344,7 @@
         <v>2015</v>
       </c>
       <c r="D791" t="s">
-        <v>3201</v>
+        <v>3200</v>
       </c>
       <c r="E791" t="s">
         <v>10</v>
@@ -33431,7 +33431,7 @@
         <v>2023</v>
       </c>
       <c r="D794" t="s">
-        <v>3202</v>
+        <v>3201</v>
       </c>
       <c r="E794" t="s">
         <v>10</v>
@@ -33460,7 +33460,7 @@
         <v>2025</v>
       </c>
       <c r="D795" t="s">
-        <v>3203</v>
+        <v>3202</v>
       </c>
       <c r="E795" t="s">
         <v>10</v>
@@ -33489,7 +33489,7 @@
         <v>2027</v>
       </c>
       <c r="D796" t="s">
-        <v>3204</v>
+        <v>3203</v>
       </c>
       <c r="E796" t="s">
         <v>10</v>
@@ -33518,7 +33518,7 @@
         <v>2029</v>
       </c>
       <c r="D797" t="s">
-        <v>3205</v>
+        <v>3204</v>
       </c>
       <c r="E797" t="s">
         <v>10</v>
@@ -33547,7 +33547,7 @@
         <v>2031</v>
       </c>
       <c r="D798" t="s">
-        <v>3206</v>
+        <v>3205</v>
       </c>
       <c r="E798" t="s">
         <v>10</v>
@@ -33576,7 +33576,7 @@
         <v>2033</v>
       </c>
       <c r="D799" t="s">
-        <v>3207</v>
+        <v>3206</v>
       </c>
       <c r="E799" t="s">
         <v>10</v>
@@ -33750,7 +33750,7 @@
         <v>2050</v>
       </c>
       <c r="D805" t="s">
-        <v>3208</v>
+        <v>3207</v>
       </c>
       <c r="E805" t="s">
         <v>10</v>
@@ -34098,7 +34098,7 @@
         <v>2085</v>
       </c>
       <c r="D817" t="s">
-        <v>3209</v>
+        <v>3208</v>
       </c>
       <c r="E817" t="s">
         <v>10</v>
@@ -34127,7 +34127,7 @@
         <v>2087</v>
       </c>
       <c r="D818" t="s">
-        <v>3210</v>
+        <v>3209</v>
       </c>
       <c r="E818" t="s">
         <v>10</v>
@@ -34156,7 +34156,7 @@
         <v>2089</v>
       </c>
       <c r="D819" t="s">
-        <v>3211</v>
+        <v>3210</v>
       </c>
       <c r="E819" t="s">
         <v>10</v>
@@ -34185,7 +34185,7 @@
         <v>2091</v>
       </c>
       <c r="D820" t="s">
-        <v>3212</v>
+        <v>3211</v>
       </c>
       <c r="E820" t="s">
         <v>10</v>
@@ -34214,7 +34214,7 @@
         <v>2093</v>
       </c>
       <c r="D821" t="s">
-        <v>3213</v>
+        <v>3212</v>
       </c>
       <c r="E821" t="s">
         <v>10</v>
@@ -34243,7 +34243,7 @@
         <v>2095</v>
       </c>
       <c r="D822" t="s">
-        <v>3214</v>
+        <v>3213</v>
       </c>
       <c r="E822" t="s">
         <v>10</v>
@@ -34272,7 +34272,7 @@
         <v>2097</v>
       </c>
       <c r="D823" t="s">
-        <v>3215</v>
+        <v>3214</v>
       </c>
       <c r="E823" t="s">
         <v>10</v>
@@ -34330,7 +34330,7 @@
         <v>2102</v>
       </c>
       <c r="D825" t="s">
-        <v>3216</v>
+        <v>3215</v>
       </c>
       <c r="E825" t="s">
         <v>10</v>
@@ -34388,7 +34388,7 @@
         <v>2107</v>
       </c>
       <c r="D827" t="s">
-        <v>3217</v>
+        <v>3216</v>
       </c>
       <c r="E827" t="s">
         <v>10</v>
@@ -34417,7 +34417,7 @@
         <v>2109</v>
       </c>
       <c r="D828" t="s">
-        <v>3218</v>
+        <v>3217</v>
       </c>
       <c r="E828" t="s">
         <v>10</v>
@@ -34446,7 +34446,7 @@
         <v>2111</v>
       </c>
       <c r="D829" t="s">
-        <v>3219</v>
+        <v>3218</v>
       </c>
       <c r="E829" t="s">
         <v>10</v>
@@ -34649,7 +34649,7 @@
         <v>2131</v>
       </c>
       <c r="D836" t="s">
-        <v>3220</v>
+        <v>3219</v>
       </c>
       <c r="E836" t="s">
         <v>10</v>
@@ -34997,7 +34997,7 @@
         <v>2166</v>
       </c>
       <c r="D848" t="s">
-        <v>3221</v>
+        <v>3220</v>
       </c>
       <c r="E848" t="s">
         <v>10</v>
@@ -35026,7 +35026,7 @@
         <v>2168</v>
       </c>
       <c r="D849" t="s">
-        <v>3222</v>
+        <v>3221</v>
       </c>
       <c r="E849" t="s">
         <v>10</v>
@@ -35055,7 +35055,7 @@
         <v>2170</v>
       </c>
       <c r="D850" t="s">
-        <v>3223</v>
+        <v>3222</v>
       </c>
       <c r="E850" t="s">
         <v>10</v>
@@ -35171,7 +35171,7 @@
         <v>2181</v>
       </c>
       <c r="D854" t="s">
-        <v>3224</v>
+        <v>3223</v>
       </c>
       <c r="E854" t="s">
         <v>10</v>
@@ -35200,7 +35200,7 @@
         <v>2183</v>
       </c>
       <c r="D855" t="s">
-        <v>3225</v>
+        <v>3224</v>
       </c>
       <c r="E855" t="s">
         <v>10</v>
@@ -35229,7 +35229,7 @@
         <v>2185</v>
       </c>
       <c r="D856" t="s">
-        <v>3226</v>
+        <v>3225</v>
       </c>
       <c r="E856" t="s">
         <v>10</v>
@@ -35258,7 +35258,7 @@
         <v>2187</v>
       </c>
       <c r="D857" t="s">
-        <v>3227</v>
+        <v>3226</v>
       </c>
       <c r="E857" t="s">
         <v>10</v>
@@ -35287,7 +35287,7 @@
         <v>2189</v>
       </c>
       <c r="D858" t="s">
-        <v>3228</v>
+        <v>3227</v>
       </c>
       <c r="E858" t="s">
         <v>10</v>
@@ -35519,7 +35519,7 @@
         <v>2212</v>
       </c>
       <c r="D866" t="s">
-        <v>3229</v>
+        <v>3228</v>
       </c>
       <c r="E866" t="s">
         <v>10</v>
@@ -35548,7 +35548,7 @@
         <v>2214</v>
       </c>
       <c r="D867" t="s">
-        <v>3230</v>
+        <v>3229</v>
       </c>
       <c r="E867" t="s">
         <v>10</v>
@@ -35577,7 +35577,7 @@
         <v>2216</v>
       </c>
       <c r="D868" t="s">
-        <v>3231</v>
+        <v>3230</v>
       </c>
       <c r="E868" t="s">
         <v>10</v>
@@ -35722,7 +35722,7 @@
         <v>2230</v>
       </c>
       <c r="D873" t="s">
-        <v>3232</v>
+        <v>3231</v>
       </c>
       <c r="E873" t="s">
         <v>10</v>
@@ -35751,7 +35751,7 @@
         <v>2232</v>
       </c>
       <c r="D874" t="s">
-        <v>3233</v>
+        <v>3232</v>
       </c>
       <c r="E874" t="s">
         <v>10</v>
@@ -35780,7 +35780,7 @@
         <v>2234</v>
       </c>
       <c r="D875" t="s">
-        <v>3234</v>
+        <v>3233</v>
       </c>
       <c r="E875" t="s">
         <v>10</v>
@@ -35809,7 +35809,7 @@
         <v>2236</v>
       </c>
       <c r="D876" t="s">
-        <v>3235</v>
+        <v>3234</v>
       </c>
       <c r="E876" t="s">
         <v>10</v>
@@ -35838,7 +35838,7 @@
         <v>2238</v>
       </c>
       <c r="D877" t="s">
-        <v>3236</v>
+        <v>3235</v>
       </c>
       <c r="E877" t="s">
         <v>10</v>
@@ -35867,7 +35867,7 @@
         <v>2240</v>
       </c>
       <c r="D878" t="s">
-        <v>3237</v>
+        <v>3236</v>
       </c>
       <c r="E878" t="s">
         <v>10</v>
@@ -35896,7 +35896,7 @@
         <v>2242</v>
       </c>
       <c r="D879" t="s">
-        <v>3238</v>
+        <v>3237</v>
       </c>
       <c r="E879" t="s">
         <v>10</v>
@@ -35983,7 +35983,7 @@
         <v>2250</v>
       </c>
       <c r="D882" t="s">
-        <v>3239</v>
+        <v>3238</v>
       </c>
       <c r="E882" t="s">
         <v>10</v>
@@ -36012,7 +36012,7 @@
         <v>2252</v>
       </c>
       <c r="D883" t="s">
-        <v>3240</v>
+        <v>3239</v>
       </c>
       <c r="E883" t="s">
         <v>10</v>
@@ -36041,7 +36041,7 @@
         <v>2254</v>
       </c>
       <c r="D884" t="s">
-        <v>3241</v>
+        <v>3240</v>
       </c>
       <c r="E884" t="s">
         <v>10</v>
@@ -36070,7 +36070,7 @@
         <v>2256</v>
       </c>
       <c r="D885" t="s">
-        <v>3242</v>
+        <v>3241</v>
       </c>
       <c r="E885" t="s">
         <v>10</v>
@@ -36099,7 +36099,7 @@
         <v>2258</v>
       </c>
       <c r="D886" t="s">
-        <v>3243</v>
+        <v>3242</v>
       </c>
       <c r="E886" t="s">
         <v>10</v>
@@ -36128,7 +36128,7 @@
         <v>2260</v>
       </c>
       <c r="D887" t="s">
-        <v>3244</v>
+        <v>3243</v>
       </c>
       <c r="E887" t="s">
         <v>10</v>
@@ -36215,7 +36215,7 @@
         <v>2268</v>
       </c>
       <c r="D890" t="s">
-        <v>3245</v>
+        <v>3244</v>
       </c>
       <c r="E890" t="s">
         <v>10</v>
@@ -36302,7 +36302,7 @@
         <v>2276</v>
       </c>
       <c r="D893" t="s">
-        <v>3246</v>
+        <v>3245</v>
       </c>
       <c r="E893" t="s">
         <v>10</v>
@@ -36331,7 +36331,7 @@
         <v>2278</v>
       </c>
       <c r="D894" t="s">
-        <v>3247</v>
+        <v>3246</v>
       </c>
       <c r="E894" t="s">
         <v>10</v>
@@ -36360,7 +36360,7 @@
         <v>2280</v>
       </c>
       <c r="D895" t="s">
-        <v>3248</v>
+        <v>3247</v>
       </c>
       <c r="E895" t="s">
         <v>10</v>
@@ -36389,7 +36389,7 @@
         <v>2282</v>
       </c>
       <c r="D896" t="s">
-        <v>3249</v>
+        <v>3248</v>
       </c>
       <c r="E896" t="s">
         <v>10</v>
@@ -36418,7 +36418,7 @@
         <v>2284</v>
       </c>
       <c r="D897" t="s">
-        <v>3250</v>
+        <v>3249</v>
       </c>
       <c r="E897" t="s">
         <v>10</v>
@@ -36795,7 +36795,7 @@
         <v>2322</v>
       </c>
       <c r="D910" t="s">
-        <v>3251</v>
+        <v>3250</v>
       </c>
       <c r="E910" t="s">
         <v>10</v>
@@ -36824,7 +36824,7 @@
         <v>2324</v>
       </c>
       <c r="D911" t="s">
-        <v>3252</v>
+        <v>3251</v>
       </c>
       <c r="E911" t="s">
         <v>10</v>
@@ -36853,7 +36853,7 @@
         <v>2326</v>
       </c>
       <c r="D912" t="s">
-        <v>3253</v>
+        <v>3252</v>
       </c>
       <c r="E912" t="s">
         <v>10</v>
@@ -37172,7 +37172,7 @@
         <v>2358</v>
       </c>
       <c r="D923" t="s">
-        <v>3254</v>
+        <v>3253</v>
       </c>
       <c r="E923" t="s">
         <v>10</v>
@@ -37201,7 +37201,7 @@
         <v>2360</v>
       </c>
       <c r="D924" t="s">
-        <v>3255</v>
+        <v>3254</v>
       </c>
       <c r="E924" t="s">
         <v>10</v>
@@ -37230,7 +37230,7 @@
         <v>2362</v>
       </c>
       <c r="D925" t="s">
-        <v>3256</v>
+        <v>3255</v>
       </c>
       <c r="E925" t="s">
         <v>10</v>
@@ -37259,7 +37259,7 @@
         <v>2364</v>
       </c>
       <c r="D926" t="s">
-        <v>3257</v>
+        <v>3256</v>
       </c>
       <c r="E926" t="s">
         <v>10</v>
@@ -37346,7 +37346,7 @@
         <v>2372</v>
       </c>
       <c r="D929" t="s">
-        <v>3258</v>
+        <v>3257</v>
       </c>
       <c r="E929" t="s">
         <v>10</v>
@@ -37375,7 +37375,7 @@
         <v>2374</v>
       </c>
       <c r="D930" t="s">
-        <v>3259</v>
+        <v>3258</v>
       </c>
       <c r="E930" t="s">
         <v>10</v>
@@ -37404,7 +37404,7 @@
         <v>2376</v>
       </c>
       <c r="D931" t="s">
-        <v>3260</v>
+        <v>3259</v>
       </c>
       <c r="E931" t="s">
         <v>10</v>
@@ -37433,7 +37433,7 @@
         <v>2378</v>
       </c>
       <c r="D932" t="s">
-        <v>3261</v>
+        <v>3260</v>
       </c>
       <c r="E932" t="s">
         <v>10</v>
@@ -37462,7 +37462,7 @@
         <v>2380</v>
       </c>
       <c r="D933" t="s">
-        <v>3262</v>
+        <v>3261</v>
       </c>
       <c r="E933" t="s">
         <v>10</v>
@@ -37520,7 +37520,7 @@
         <v>2385</v>
       </c>
       <c r="D935" t="s">
-        <v>3263</v>
+        <v>3262</v>
       </c>
       <c r="E935" t="s">
         <v>10</v>
@@ -37549,7 +37549,7 @@
         <v>2387</v>
       </c>
       <c r="D936" t="s">
-        <v>3264</v>
+        <v>3263</v>
       </c>
       <c r="E936" t="s">
         <v>10</v>
@@ -37578,7 +37578,7 @@
         <v>2389</v>
       </c>
       <c r="D937" t="s">
-        <v>3265</v>
+        <v>3264</v>
       </c>
       <c r="E937" t="s">
         <v>10</v>
@@ -37665,7 +37665,7 @@
         <v>2397</v>
       </c>
       <c r="D940" t="s">
-        <v>3266</v>
+        <v>3265</v>
       </c>
       <c r="E940" t="s">
         <v>10</v>
@@ -37694,7 +37694,7 @@
         <v>2399</v>
       </c>
       <c r="D941" t="s">
-        <v>3267</v>
+        <v>3266</v>
       </c>
       <c r="E941" t="s">
         <v>10</v>
@@ -37723,7 +37723,7 @@
         <v>2401</v>
       </c>
       <c r="D942" t="s">
-        <v>3268</v>
+        <v>3267</v>
       </c>
       <c r="E942" t="s">
         <v>10</v>
@@ -38042,7 +38042,7 @@
         <v>2433</v>
       </c>
       <c r="D953" t="s">
-        <v>3269</v>
+        <v>3268</v>
       </c>
       <c r="E953" t="s">
         <v>10</v>
@@ -38071,7 +38071,7 @@
         <v>2435</v>
       </c>
       <c r="D954" t="s">
-        <v>3270</v>
+        <v>3269</v>
       </c>
       <c r="E954" t="s">
         <v>10</v>
@@ -38100,7 +38100,7 @@
         <v>2437</v>
       </c>
       <c r="D955" t="s">
-        <v>3271</v>
+        <v>3270</v>
       </c>
       <c r="E955" t="s">
         <v>10</v>
@@ -38158,7 +38158,7 @@
         <v>2442</v>
       </c>
       <c r="D957" t="s">
-        <v>3272</v>
+        <v>3271</v>
       </c>
       <c r="E957" t="s">
         <v>10</v>
@@ -38187,7 +38187,7 @@
         <v>2444</v>
       </c>
       <c r="D958" t="s">
-        <v>3273</v>
+        <v>3272</v>
       </c>
       <c r="E958" t="s">
         <v>10</v>
@@ -38216,7 +38216,7 @@
         <v>2446</v>
       </c>
       <c r="D959" t="s">
-        <v>3274</v>
+        <v>3273</v>
       </c>
       <c r="E959" t="s">
         <v>10</v>
@@ -38245,7 +38245,7 @@
         <v>2448</v>
       </c>
       <c r="D960" t="s">
-        <v>3275</v>
+        <v>3274</v>
       </c>
       <c r="E960" t="s">
         <v>10</v>
@@ -38390,7 +38390,7 @@
         <v>2462</v>
       </c>
       <c r="D965" t="s">
-        <v>3276</v>
+        <v>3275</v>
       </c>
       <c r="E965" t="s">
         <v>10</v>
@@ -38419,7 +38419,7 @@
         <v>2464</v>
       </c>
       <c r="D966" t="s">
-        <v>3277</v>
+        <v>3276</v>
       </c>
       <c r="E966" t="s">
         <v>10</v>
@@ -38448,7 +38448,7 @@
         <v>2466</v>
       </c>
       <c r="D967" t="s">
-        <v>3278</v>
+        <v>3277</v>
       </c>
       <c r="E967" t="s">
         <v>10</v>
@@ -38477,7 +38477,7 @@
         <v>2468</v>
       </c>
       <c r="D968" t="s">
-        <v>3279</v>
+        <v>3278</v>
       </c>
       <c r="E968" t="s">
         <v>10</v>
@@ -38535,7 +38535,7 @@
         <v>2473</v>
       </c>
       <c r="D970" t="s">
-        <v>3280</v>
+        <v>3279</v>
       </c>
       <c r="E970" t="s">
         <v>10</v>
@@ -38564,7 +38564,7 @@
         <v>2475</v>
       </c>
       <c r="D971" t="s">
-        <v>3281</v>
+        <v>3280</v>
       </c>
       <c r="E971" t="s">
         <v>10</v>
@@ -38593,7 +38593,7 @@
         <v>2477</v>
       </c>
       <c r="D972" t="s">
-        <v>3282</v>
+        <v>3281</v>
       </c>
       <c r="E972" t="s">
         <v>10</v>
@@ -38622,7 +38622,7 @@
         <v>2479</v>
       </c>
       <c r="D973" t="s">
-        <v>3283</v>
+        <v>3282</v>
       </c>
       <c r="E973" t="s">
         <v>10</v>
@@ -38651,7 +38651,7 @@
         <v>2481</v>
       </c>
       <c r="D974" t="s">
-        <v>3284</v>
+        <v>3283</v>
       </c>
       <c r="E974" t="s">
         <v>10</v>
@@ -38680,7 +38680,7 @@
         <v>2483</v>
       </c>
       <c r="D975" t="s">
-        <v>3285</v>
+        <v>3284</v>
       </c>
       <c r="E975" t="s">
         <v>10</v>
@@ -38883,7 +38883,7 @@
         <v>2503</v>
       </c>
       <c r="D982" t="s">
-        <v>3286</v>
+        <v>3285</v>
       </c>
       <c r="E982" t="s">
         <v>10</v>
@@ -38999,7 +38999,7 @@
         <v>2514</v>
       </c>
       <c r="D986" t="s">
-        <v>3287</v>
+        <v>3286</v>
       </c>
       <c r="E986" t="s">
         <v>10</v>
@@ -39028,7 +39028,7 @@
         <v>2516</v>
       </c>
       <c r="D987" t="s">
-        <v>3288</v>
+        <v>3287</v>
       </c>
       <c r="E987" t="s">
         <v>10</v>
@@ -39057,7 +39057,7 @@
         <v>2518</v>
       </c>
       <c r="D988" t="s">
-        <v>3289</v>
+        <v>3288</v>
       </c>
       <c r="E988" t="s">
         <v>10</v>
@@ -39086,7 +39086,7 @@
         <v>2520</v>
       </c>
       <c r="D989" t="s">
-        <v>3290</v>
+        <v>3289</v>
       </c>
       <c r="E989" t="s">
         <v>10</v>
@@ -39115,7 +39115,7 @@
         <v>2522</v>
       </c>
       <c r="D990" t="s">
-        <v>3291</v>
+        <v>3290</v>
       </c>
       <c r="E990" t="s">
         <v>10</v>
@@ -39231,7 +39231,7 @@
         <v>2533</v>
       </c>
       <c r="D994" t="s">
-        <v>3292</v>
+        <v>3291</v>
       </c>
       <c r="E994" t="s">
         <v>10</v>
@@ -39347,7 +39347,7 @@
         <v>2544</v>
       </c>
       <c r="D998" t="s">
-        <v>3293</v>
+        <v>3292</v>
       </c>
       <c r="E998" t="s">
         <v>10</v>
@@ -39376,7 +39376,7 @@
         <v>2546</v>
       </c>
       <c r="D999" t="s">
-        <v>3294</v>
+        <v>3293</v>
       </c>
       <c r="E999" t="s">
         <v>10</v>
@@ -39550,7 +39550,7 @@
         <v>2563</v>
       </c>
       <c r="D1005" t="s">
-        <v>3295</v>
+        <v>3294</v>
       </c>
       <c r="E1005" t="s">
         <v>10</v>
@@ -39579,7 +39579,7 @@
         <v>2565</v>
       </c>
       <c r="D1006" t="s">
-        <v>3296</v>
+        <v>3295</v>
       </c>
       <c r="E1006" t="s">
         <v>10</v>
@@ -39608,7 +39608,7 @@
         <v>2567</v>
       </c>
       <c r="D1007" t="s">
-        <v>3297</v>
+        <v>3296</v>
       </c>
       <c r="E1007" t="s">
         <v>10</v>
@@ -39637,7 +39637,7 @@
         <v>2569</v>
       </c>
       <c r="D1008" t="s">
-        <v>3298</v>
+        <v>3297</v>
       </c>
       <c r="E1008" t="s">
         <v>10</v>
@@ -39666,7 +39666,7 @@
         <v>2571</v>
       </c>
       <c r="D1009" t="s">
-        <v>3299</v>
+        <v>3298</v>
       </c>
       <c r="E1009" t="s">
         <v>10</v>
@@ -39695,7 +39695,7 @@
         <v>2573</v>
       </c>
       <c r="D1010" t="s">
-        <v>3300</v>
+        <v>3299</v>
       </c>
       <c r="E1010" t="s">
         <v>10</v>
@@ -39811,7 +39811,7 @@
         <v>2584</v>
       </c>
       <c r="D1014" t="s">
-        <v>3301</v>
+        <v>3300</v>
       </c>
       <c r="E1014" t="s">
         <v>10</v>
@@ -39840,7 +39840,7 @@
         <v>2586</v>
       </c>
       <c r="D1015" t="s">
-        <v>3302</v>
+        <v>3301</v>
       </c>
       <c r="E1015" t="s">
         <v>10</v>
@@ -39869,7 +39869,7 @@
         <v>2588</v>
       </c>
       <c r="D1016" t="s">
-        <v>3303</v>
+        <v>3302</v>
       </c>
       <c r="E1016" t="s">
         <v>10</v>
@@ -39898,7 +39898,7 @@
         <v>2590</v>
       </c>
       <c r="D1017" t="s">
-        <v>3304</v>
+        <v>3303</v>
       </c>
       <c r="E1017" t="s">
         <v>10</v>
@@ -40043,7 +40043,7 @@
         <v>2604</v>
       </c>
       <c r="D1022" t="s">
-        <v>3305</v>
+        <v>3304</v>
       </c>
       <c r="E1022" t="s">
         <v>10</v>
@@ -40072,7 +40072,7 @@
         <v>2606</v>
       </c>
       <c r="D1023" t="s">
-        <v>3306</v>
+        <v>3305</v>
       </c>
       <c r="E1023" t="s">
         <v>10</v>
@@ -40101,7 +40101,7 @@
         <v>2608</v>
       </c>
       <c r="D1024" t="s">
-        <v>3307</v>
+        <v>3306</v>
       </c>
       <c r="E1024" t="s">
         <v>10</v>
@@ -40130,7 +40130,7 @@
         <v>2610</v>
       </c>
       <c r="D1025" t="s">
-        <v>3308</v>
+        <v>3307</v>
       </c>
       <c r="E1025" t="s">
         <v>10</v>
@@ -40275,7 +40275,7 @@
         <v>2624</v>
       </c>
       <c r="D1030" t="s">
-        <v>3309</v>
+        <v>3308</v>
       </c>
       <c r="E1030" t="s">
         <v>10</v>
@@ -40507,7 +40507,7 @@
         <v>2647</v>
       </c>
       <c r="D1038" t="s">
-        <v>3310</v>
+        <v>3309</v>
       </c>
       <c r="E1038" t="s">
         <v>10</v>
@@ -40536,7 +40536,7 @@
         <v>2649</v>
       </c>
       <c r="D1039" t="s">
-        <v>3311</v>
+        <v>3310</v>
       </c>
       <c r="E1039" t="s">
         <v>10</v>
@@ -40623,7 +40623,7 @@
         <v>2657</v>
       </c>
       <c r="D1042" t="s">
-        <v>3312</v>
+        <v>3311</v>
       </c>
       <c r="E1042" t="s">
         <v>10</v>
@@ -40681,7 +40681,7 @@
         <v>2662</v>
       </c>
       <c r="D1044" t="s">
-        <v>3313</v>
+        <v>3312</v>
       </c>
       <c r="E1044" t="s">
         <v>10</v>
@@ -40710,7 +40710,7 @@
         <v>2664</v>
       </c>
       <c r="D1045" t="s">
-        <v>3314</v>
+        <v>3313</v>
       </c>
       <c r="E1045" t="s">
         <v>10</v>
@@ -40739,7 +40739,7 @@
         <v>2666</v>
       </c>
       <c r="D1046" t="s">
-        <v>3315</v>
+        <v>3314</v>
       </c>
       <c r="E1046" t="s">
         <v>10</v>
@@ -40826,7 +40826,7 @@
         <v>2674</v>
       </c>
       <c r="D1049" t="s">
-        <v>3316</v>
+        <v>3315</v>
       </c>
       <c r="E1049" t="s">
         <v>10</v>
@@ -40913,7 +40913,7 @@
         <v>2682</v>
       </c>
       <c r="D1052" t="s">
-        <v>3317</v>
+        <v>3316</v>
       </c>
       <c r="E1052" t="s">
         <v>10</v>
@@ -40942,7 +40942,7 @@
         <v>2684</v>
       </c>
       <c r="D1053" t="s">
-        <v>3318</v>
+        <v>3317</v>
       </c>
       <c r="E1053" t="s">
         <v>10</v>
@@ -41145,7 +41145,7 @@
         <v>2704</v>
       </c>
       <c r="D1060" t="s">
-        <v>3319</v>
+        <v>3318</v>
       </c>
       <c r="E1060" t="s">
         <v>10</v>
@@ -41203,7 +41203,7 @@
         <v>2709</v>
       </c>
       <c r="D1062" t="s">
-        <v>3320</v>
+        <v>3319</v>
       </c>
       <c r="E1062" t="s">
         <v>10</v>
@@ -41232,7 +41232,7 @@
         <v>2711</v>
       </c>
       <c r="D1063" t="s">
-        <v>3321</v>
+        <v>3320</v>
       </c>
       <c r="E1063" t="s">
         <v>10</v>
@@ -41261,7 +41261,7 @@
         <v>2713</v>
       </c>
       <c r="D1064" t="s">
-        <v>3322</v>
+        <v>3321</v>
       </c>
       <c r="E1064" t="s">
         <v>10</v>
@@ -41290,7 +41290,7 @@
         <v>2715</v>
       </c>
       <c r="D1065" t="s">
-        <v>3323</v>
+        <v>3322</v>
       </c>
       <c r="E1065" t="s">
         <v>10</v>
@@ -41319,7 +41319,7 @@
         <v>2717</v>
       </c>
       <c r="D1066" t="s">
-        <v>3324</v>
+        <v>3323</v>
       </c>
       <c r="E1066" t="s">
         <v>10</v>
@@ -41348,7 +41348,7 @@
         <v>2719</v>
       </c>
       <c r="D1067" t="s">
-        <v>3325</v>
+        <v>3324</v>
       </c>
       <c r="E1067" t="s">
         <v>10</v>
@@ -41377,7 +41377,7 @@
         <v>2721</v>
       </c>
       <c r="D1068" t="s">
-        <v>3326</v>
+        <v>3325</v>
       </c>
       <c r="E1068" t="s">
         <v>10</v>
@@ -41406,7 +41406,7 @@
         <v>2723</v>
       </c>
       <c r="D1069" t="s">
-        <v>3327</v>
+        <v>3326</v>
       </c>
       <c r="E1069" t="s">
         <v>10</v>
@@ -41435,7 +41435,7 @@
         <v>2725</v>
       </c>
       <c r="D1070" t="s">
-        <v>3328</v>
+        <v>3327</v>
       </c>
       <c r="E1070" t="s">
         <v>10</v>
@@ -41464,7 +41464,7 @@
         <v>2727</v>
       </c>
       <c r="D1071" t="s">
-        <v>3329</v>
+        <v>3328</v>
       </c>
       <c r="E1071" t="s">
         <v>10</v>
@@ -41493,7 +41493,7 @@
         <v>2729</v>
       </c>
       <c r="D1072" t="s">
-        <v>3330</v>
+        <v>3329</v>
       </c>
       <c r="E1072" t="s">
         <v>10</v>
@@ -41522,7 +41522,7 @@
         <v>2731</v>
       </c>
       <c r="D1073" t="s">
-        <v>3331</v>
+        <v>3330</v>
       </c>
       <c r="E1073" t="s">
         <v>10</v>
@@ -41551,7 +41551,7 @@
         <v>2733</v>
       </c>
       <c r="D1074" t="s">
-        <v>3332</v>
+        <v>3331</v>
       </c>
       <c r="E1074" t="s">
         <v>10</v>
@@ -41580,7 +41580,7 @@
         <v>2735</v>
       </c>
       <c r="D1075" t="s">
-        <v>3333</v>
+        <v>3332</v>
       </c>
       <c r="E1075" t="s">
         <v>10</v>
@@ -41725,7 +41725,7 @@
         <v>2749</v>
       </c>
       <c r="D1080" t="s">
-        <v>3334</v>
+        <v>3333</v>
       </c>
       <c r="E1080" t="s">
         <v>10</v>
@@ -41841,7 +41841,7 @@
         <v>2760</v>
       </c>
       <c r="D1084" t="s">
-        <v>3335</v>
+        <v>3334</v>
       </c>
       <c r="E1084" t="s">
         <v>10</v>
@@ -42421,7 +42421,7 @@
         <v>2819</v>
       </c>
       <c r="D1104" t="s">
-        <v>3336</v>
+        <v>3335</v>
       </c>
       <c r="E1104" t="s">
         <v>10</v>
@@ -42450,7 +42450,7 @@
         <v>2821</v>
       </c>
       <c r="D1105" t="s">
-        <v>3337</v>
+        <v>3336</v>
       </c>
       <c r="E1105" t="s">
         <v>10</v>
@@ -42479,7 +42479,7 @@
         <v>2823</v>
       </c>
       <c r="D1106" t="s">
-        <v>3338</v>
+        <v>3337</v>
       </c>
       <c r="E1106" t="s">
         <v>10</v>
